--- a/testdata/100 test data.xlsx
+++ b/testdata/100 test data.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xuan2\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xuan2\Desktop\sidequests\CeFest-Form-Processing\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B2F9E0E-C1EF-4E97-BE19-16B306A5A8D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E67FA73-B9D6-45BC-9279-C4C8C987F5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="406">
   <si>
     <t>ID</t>
   </si>
@@ -59,9 +72,6 @@
     <t>What house are you from ? </t>
   </si>
   <si>
-    <t>What is your gender ? </t>
-  </si>
-  <si>
     <t>What is your faculty and major?</t>
   </si>
   <si>
@@ -74,9 +84,6 @@
     <t>Third Choice </t>
   </si>
   <si>
-    <t>Why did you select your chosen trails ? (EG: T1 because .....) </t>
-  </si>
-  <si>
     <t>I agree</t>
   </si>
   <si>
@@ -86,12 +93,6 @@
     <t>Male</t>
   </si>
   <si>
-    <t>e1527740@u.nus.edu</t>
-  </si>
-  <si>
-    <t>Yu Hoe Tan</t>
-  </si>
-  <si>
     <t>Prefer not to say</t>
   </si>
   <si>
@@ -158,9 +159,6 @@
     <t>e1536463@u.nus.edu</t>
   </si>
   <si>
-    <t>Si Koh</t>
-  </si>
-  <si>
     <t>@testdata5</t>
   </si>
   <si>
@@ -1248,20 +1246,32 @@
   </si>
   <si>
     <t>@testdata125</t>
+  </si>
+  <si>
+    <t>What is your gender ?</t>
+  </si>
+  <si>
+    <t>Why did you select your first three trail choices ? (e.g. trail 1 - ...., trail 2- ....)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+  <numFmts count="1">
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1306,71 +1316,16 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1384,27 +1339,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:R2" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:R2" insertRow="1" totalsRowShown="0">
   <autoFilter ref="A1:R2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Last modified time" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="2" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="What is your full name?" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="What is your Telegram Handle? (eg. @ilovecefest)_x000a_" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="What is your NUS E......@u.nus.edu email ? " dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="I am currently... (in AY26/27)" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="What house are you from ? " dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="What is your gender ? " dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="What is your faculty and major?" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="First Choice " dataDxfId="3"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Second Choice " dataDxfId="2"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Third Choice " dataDxfId="1"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Why did you select your chosen trails ? (EG: T1 because .....) " dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Last modified time"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="What is your full name?"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="What is your Telegram Handle? (eg. @ilovecefest)_x000a_"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="What is your NUS E......@u.nus.edu email ? "/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="I am currently... (in AY26/27)"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="What house are you from ? "/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="What is your gender ?"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="What is your faculty and major?"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="First Choice "/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Second Choice "/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Third Choice "/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Why did you select your first three trail choices ? (e.g. trail 1 - ...., trail 2- ....)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1708,12 +1663,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R127"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="18" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1732,7 +1687,7 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
@@ -1751,6180 +1706,6314 @@
         <v>11</v>
       </c>
       <c r="M1" t="s">
+        <v>404</v>
+      </c>
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A2">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1">
-        <v>46164.640034722222</v>
-      </c>
-      <c r="C2" s="1">
-        <v>46164.640057870369</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="R1" s="5" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>46164.575694444437</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>46164.57708333333</v>
       </c>
       <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="str">
+        <f xml:space="preserve"> _xlfn.CONCAT( "TEST - ", E3)</f>
+        <v>TEST - Jia Tan</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" t="s">
+      <c r="M3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" t="s">
         <v>28</v>
       </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="O3" t="s">
         <v>29</v>
       </c>
-      <c r="J3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="P3" t="s">
         <v>30</v>
       </c>
-      <c r="L3" t="s">
+      <c r="Q3" t="s">
         <v>31</v>
       </c>
-      <c r="M3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="R3" t="s">
         <v>32</v>
       </c>
-      <c r="O3" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>46164.578472222223</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>46164.581944444442</v>
       </c>
       <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" ref="H4:H67" si="0" xml:space="preserve"> _xlfn.CONCAT( "TEST - ", E4)</f>
+        <v>TEST - Sarah Tan</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+      <c r="M4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" t="s">
         <v>37</v>
       </c>
-      <c r="E4" t="s">
+      <c r="P4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q4" t="s">
         <v>38</v>
       </c>
-      <c r="G4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I4" s="5" t="s">
+      <c r="R4" t="s">
         <v>39</v>
       </c>
-      <c r="J4" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" t="s">
-        <v>23</v>
-      </c>
-      <c r="N4" t="s">
-        <v>40</v>
-      </c>
-      <c r="O4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>42</v>
-      </c>
-      <c r="R4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>46164.584027777782</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>46164.585416666669</v>
       </c>
       <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">TEST - </v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s">
         <v>44</v>
       </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="O5" t="s">
         <v>45</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="P5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" t="s">
         <v>46</v>
       </c>
-      <c r="J5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="R5" t="s">
         <v>47</v>
       </c>
-      <c r="L5" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" t="s">
-        <v>48</v>
-      </c>
-      <c r="N5" t="s">
-        <v>49</v>
-      </c>
-      <c r="O5" t="s">
-        <v>50</v>
-      </c>
-      <c r="P5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>51</v>
-      </c>
-      <c r="R5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>46164.587500000001</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>46164.59097222222</v>
       </c>
       <c r="D6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Rui Lim</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K6" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" t="s">
         <v>53</v>
       </c>
-      <c r="E6" t="s">
+      <c r="O6" t="s">
+        <v>29</v>
+      </c>
+      <c r="P6" t="s">
         <v>54</v>
       </c>
-      <c r="G6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="J6" t="s">
-        <v>53</v>
-      </c>
-      <c r="K6" t="s">
-        <v>56</v>
-      </c>
-      <c r="L6" t="s">
-        <v>57</v>
-      </c>
-      <c r="M6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N6" t="s">
-        <v>58</v>
-      </c>
-      <c r="O6" t="s">
-        <v>33</v>
-      </c>
-      <c r="P6" t="s">
-        <v>59</v>
-      </c>
       <c r="Q6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="R6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>46164.59375</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>46164.595138888893</v>
       </c>
       <c r="D7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Ting Wong</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O7" t="s">
+        <v>20</v>
+      </c>
+      <c r="P7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>46</v>
+      </c>
+      <c r="R7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" t="s">
-        <v>61</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J7" t="s">
-        <v>60</v>
-      </c>
-      <c r="K7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" t="s">
-        <v>63</v>
-      </c>
-      <c r="M7" t="s">
-        <v>48</v>
-      </c>
-      <c r="N7" t="s">
-        <v>64</v>
-      </c>
-      <c r="O7" t="s">
-        <v>24</v>
-      </c>
-      <c r="P7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>51</v>
-      </c>
-      <c r="R7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>46164.598611111112</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>46164.6</v>
       </c>
       <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Sarah Lim</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="J8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O8" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>46</v>
+      </c>
+      <c r="R8" t="s">
         <v>66</v>
       </c>
-      <c r="E8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="J8" t="s">
-        <v>66</v>
-      </c>
-      <c r="K8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L8" t="s">
-        <v>19</v>
-      </c>
-      <c r="M8" t="s">
-        <v>48</v>
-      </c>
-      <c r="N8" t="s">
-        <v>32</v>
-      </c>
-      <c r="O8" t="s">
-        <v>69</v>
-      </c>
-      <c r="P8" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>51</v>
-      </c>
-      <c r="R8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>46164.602777777778</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>46164.605555555558</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>74</v>
+        <v>16</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Kai Lee</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="J9" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="K9" t="s">
+        <v>42</v>
+      </c>
+      <c r="L9" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" t="s">
+        <v>19</v>
+      </c>
+      <c r="N9" t="s">
+        <v>70</v>
+      </c>
+      <c r="O9" t="s">
+        <v>45</v>
+      </c>
+      <c r="P9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R9" t="s">
         <v>47</v>
       </c>
-      <c r="L9" t="s">
-        <v>31</v>
-      </c>
-      <c r="M9" t="s">
-        <v>23</v>
-      </c>
-      <c r="N9" t="s">
-        <v>75</v>
-      </c>
-      <c r="O9" t="s">
-        <v>50</v>
-      </c>
-      <c r="P9" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>42</v>
-      </c>
-      <c r="R9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>46164.607638888891</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>46164.611111111109</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" t="s">
-        <v>77</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>78</v>
+        <v>16</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Jia Patel</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="J10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K10" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N10" t="s">
+        <v>59</v>
+      </c>
+      <c r="O10" t="s">
+        <v>46</v>
+      </c>
+      <c r="P10" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q10" t="s">
         <v>64</v>
       </c>
-      <c r="O10" t="s">
-        <v>51</v>
-      </c>
-      <c r="P10" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>69</v>
-      </c>
       <c r="R10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>46164.614583333343</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>46164.617361111108</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Ethan Williams</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J11" t="s">
+        <v>75</v>
+      </c>
+      <c r="K11" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" t="s">
         <v>18</v>
       </c>
-      <c r="H11" t="s">
-        <v>81</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="J11" t="s">
-        <v>80</v>
-      </c>
-      <c r="K11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L11" t="s">
-        <v>31</v>
-      </c>
-      <c r="M11" t="s">
-        <v>20</v>
-      </c>
       <c r="N11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="O11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="Q11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="R11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <v>46164.616666666669</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>46164.618055555547</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>85</v>
+        <v>16</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Ming Goh</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="J12" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" t="s">
+        <v>19</v>
+      </c>
+      <c r="N12" t="s">
+        <v>28</v>
+      </c>
+      <c r="O12" t="s">
+        <v>38</v>
+      </c>
+      <c r="P12" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q12" t="s">
         <v>30</v>
       </c>
-      <c r="L12" t="s">
-        <v>63</v>
-      </c>
-      <c r="M12" t="s">
-        <v>23</v>
-      </c>
-      <c r="N12" t="s">
-        <v>32</v>
-      </c>
-      <c r="O12" t="s">
-        <v>42</v>
-      </c>
-      <c r="P12" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>34</v>
-      </c>
       <c r="R12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="2">
         <v>46164.624305555553</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
         <v>46164.627083333333</v>
       </c>
       <c r="D13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Aisha Lee</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J13" t="s">
+        <v>82</v>
+      </c>
+      <c r="K13" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" t="s">
+        <v>52</v>
+      </c>
+      <c r="M13" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" t="s">
+        <v>70</v>
+      </c>
+      <c r="O13" t="s">
+        <v>86</v>
+      </c>
+      <c r="P13" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>54</v>
+      </c>
+      <c r="R13" t="s">
         <v>87</v>
       </c>
-      <c r="E13" t="s">
-        <v>88</v>
-      </c>
-      <c r="G13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" t="s">
-        <v>88</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="J13" t="s">
-        <v>87</v>
-      </c>
-      <c r="K13" t="s">
-        <v>90</v>
-      </c>
-      <c r="L13" t="s">
-        <v>57</v>
-      </c>
-      <c r="M13" t="s">
-        <v>48</v>
-      </c>
-      <c r="N13" t="s">
-        <v>75</v>
-      </c>
-      <c r="O13" t="s">
-        <v>91</v>
-      </c>
-      <c r="P13" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>59</v>
-      </c>
-      <c r="R13" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <v>46164.627083333333</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <v>46164.630555555559</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" t="s">
-        <v>94</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>95</v>
+        <v>16</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Raj Tan</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="J14" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L14" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M14" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N14" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="O14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P14" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q14" t="s">
+        <v>86</v>
+      </c>
+      <c r="R14" t="s">
         <v>91</v>
       </c>
-      <c r="R14" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="2">
         <v>46164.634027777778</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <v>46164.636111111111</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" t="s">
-        <v>98</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>99</v>
+        <v>16</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Priya Williams</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="J15" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" t="s">
+        <v>52</v>
+      </c>
+      <c r="M15" t="s">
+        <v>43</v>
+      </c>
+      <c r="N15" t="s">
+        <v>36</v>
+      </c>
+      <c r="O15" t="s">
         <v>30</v>
       </c>
-      <c r="L15" t="s">
-        <v>57</v>
-      </c>
-      <c r="M15" t="s">
-        <v>48</v>
-      </c>
-      <c r="N15" t="s">
-        <v>40</v>
-      </c>
-      <c r="O15" t="s">
-        <v>34</v>
-      </c>
       <c r="P15" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q15" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="R15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <v>46164.636111111111</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="2">
         <v>46164.638888888891</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G16" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" t="s">
-        <v>101</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>102</v>
+        <v>22</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Qi Sharma</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="J16" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K16" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M16" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N16" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="O16" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="P16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="Q16" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="R16" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="2">
         <v>46164.64166666667</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <v>46164.645138888889</v>
       </c>
       <c r="D17" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Ming Tan</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J17" t="s">
+        <v>100</v>
+      </c>
+      <c r="K17" t="s">
+        <v>85</v>
+      </c>
+      <c r="L17" t="s">
+        <v>103</v>
+      </c>
+      <c r="M17" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" t="s">
+        <v>104</v>
+      </c>
+      <c r="O17" t="s">
+        <v>30</v>
+      </c>
+      <c r="P17" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>21</v>
+      </c>
+      <c r="R17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>46164.647222222222</v>
+      </c>
+      <c r="C18" s="2">
+        <v>46164.650694444441</v>
+      </c>
+      <c r="D18" t="s">
         <v>105</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E18" t="s">
         <v>106</v>
       </c>
-      <c r="G17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17" t="s">
-        <v>106</v>
-      </c>
-      <c r="I17" s="4" t="s">
+      <c r="G18" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Qi Wong</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J18" t="s">
         <v>105</v>
       </c>
-      <c r="K17" t="s">
-        <v>90</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="K18" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" t="s">
+        <v>17</v>
+      </c>
+      <c r="M18" t="s">
+        <v>19</v>
+      </c>
+      <c r="N18" t="s">
+        <v>36</v>
+      </c>
+      <c r="O18" t="s">
+        <v>65</v>
+      </c>
+      <c r="P18" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>46</v>
+      </c>
+      <c r="R18" t="s">
         <v>108</v>
       </c>
-      <c r="M17" t="s">
-        <v>20</v>
-      </c>
-      <c r="N17" t="s">
-        <v>109</v>
-      </c>
-      <c r="O17" t="s">
-        <v>34</v>
-      </c>
-      <c r="P17" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>25</v>
-      </c>
-      <c r="R17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3">
-        <v>46164.647222222222</v>
-      </c>
-      <c r="C18" s="3">
-        <v>46164.650694444441</v>
-      </c>
-      <c r="D18" t="s">
-        <v>110</v>
-      </c>
-      <c r="E18" t="s">
-        <v>111</v>
-      </c>
-      <c r="G18" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18" t="s">
-        <v>111</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="J18" t="s">
-        <v>110</v>
-      </c>
-      <c r="K18" t="s">
-        <v>30</v>
-      </c>
-      <c r="L18" t="s">
-        <v>19</v>
-      </c>
-      <c r="M18" t="s">
-        <v>23</v>
-      </c>
-      <c r="N18" t="s">
-        <v>40</v>
-      </c>
-      <c r="O18" t="s">
-        <v>70</v>
-      </c>
-      <c r="P18" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>51</v>
-      </c>
-      <c r="R18" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="2">
         <v>46164.650694444441</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="2">
         <v>46164.652777777781</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E19" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H19" t="s">
-        <v>115</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>116</v>
+        <v>16</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Kai Chen</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="J19" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="K19" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L19" t="s">
+        <v>17</v>
+      </c>
+      <c r="M19" t="s">
         <v>19</v>
       </c>
-      <c r="M19" t="s">
-        <v>23</v>
-      </c>
       <c r="N19" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O19" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P19" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q19" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="R19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="2">
         <v>46164.658333333333</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="2">
         <v>46164.660416666673</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E20" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H20" t="s">
-        <v>119</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>120</v>
+        <v>16</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Si Tan</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="J20" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20" t="s">
+        <v>103</v>
+      </c>
+      <c r="M20" t="s">
+        <v>19</v>
+      </c>
+      <c r="N20" t="s">
+        <v>59</v>
+      </c>
+      <c r="O20" t="s">
+        <v>20</v>
+      </c>
+      <c r="P20" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q20" t="s">
         <v>30</v>
       </c>
-      <c r="L20" t="s">
-        <v>108</v>
-      </c>
-      <c r="M20" t="s">
-        <v>23</v>
-      </c>
-      <c r="N20" t="s">
-        <v>64</v>
-      </c>
-      <c r="O20" t="s">
-        <v>24</v>
-      </c>
-      <c r="P20" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>34</v>
-      </c>
       <c r="R20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="2">
         <v>46164.661111111112</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="2">
         <v>46164.662499999999</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G21" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Arjun Chua</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J21" t="s">
+        <v>116</v>
+      </c>
+      <c r="K21" t="s">
+        <v>42</v>
+      </c>
+      <c r="L21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" t="s">
         <v>18</v>
       </c>
-      <c r="H21" t="s">
-        <v>122</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="J21" t="s">
-        <v>121</v>
-      </c>
-      <c r="K21" t="s">
-        <v>47</v>
-      </c>
-      <c r="L21" t="s">
-        <v>31</v>
-      </c>
-      <c r="M21" t="s">
-        <v>20</v>
-      </c>
       <c r="N21" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O21" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="P21" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="Q21" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.45">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="2">
         <v>46164.665277777778</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="2">
         <v>46164.666666666657</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" t="s">
-        <v>125</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>126</v>
+        <v>16</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Aisha Goh</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="J22" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="K22" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M22" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N22" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="O22" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="P22" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q22" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R22" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="2">
         <v>46164.67083333333</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="2">
         <v>46164.673611111109</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Vikram Chen</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J23" t="s">
+        <v>123</v>
+      </c>
+      <c r="K23" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" t="s">
         <v>18</v>
       </c>
-      <c r="H23" t="s">
-        <v>129</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="J23" t="s">
-        <v>128</v>
-      </c>
-      <c r="K23" t="s">
-        <v>30</v>
-      </c>
-      <c r="L23" t="s">
-        <v>31</v>
-      </c>
-      <c r="M23" t="s">
-        <v>20</v>
-      </c>
       <c r="N23" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="O23" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="P23" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q23" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R23" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="2">
         <v>46164.675000000003</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="2">
         <v>46164.677083333343</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E24" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Ming Patel</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="J24" t="s">
+        <v>127</v>
+      </c>
+      <c r="K24" t="s">
+        <v>85</v>
+      </c>
+      <c r="L24" t="s">
+        <v>52</v>
+      </c>
+      <c r="M24" t="s">
         <v>18</v>
       </c>
-      <c r="H24" t="s">
-        <v>133</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="J24" t="s">
-        <v>132</v>
-      </c>
-      <c r="K24" t="s">
-        <v>90</v>
-      </c>
-      <c r="L24" t="s">
-        <v>57</v>
-      </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
+        <v>53</v>
+      </c>
+      <c r="O24" t="s">
+        <v>31</v>
+      </c>
+      <c r="P24" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q24" t="s">
         <v>20</v>
       </c>
-      <c r="N24" t="s">
-        <v>58</v>
-      </c>
-      <c r="O24" t="s">
-        <v>35</v>
-      </c>
-      <c r="P24" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>24</v>
-      </c>
       <c r="R24" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="2">
         <v>46164.681250000001</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="2">
         <v>46164.68472222222</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E25" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G25" t="s">
-        <v>18</v>
-      </c>
-      <c r="H25" t="s">
-        <v>136</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>137</v>
+        <v>16</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Rui Chua</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>132</v>
       </c>
       <c r="J25" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K25" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M25" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N25" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="O25" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="P25" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q25" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R25" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="2">
         <v>46164.6875</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="2">
         <v>46164.688888888893</v>
       </c>
       <c r="D26" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Rong Singh</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="J26" t="s">
+        <v>133</v>
+      </c>
+      <c r="K26" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" t="s">
+        <v>17</v>
+      </c>
+      <c r="M26" t="s">
         <v>18</v>
       </c>
-      <c r="H26" t="s">
-        <v>139</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="J26" t="s">
-        <v>138</v>
-      </c>
-      <c r="K26" t="s">
-        <v>30</v>
-      </c>
-      <c r="L26" t="s">
-        <v>19</v>
-      </c>
-      <c r="M26" t="s">
+      <c r="N26" t="s">
+        <v>112</v>
+      </c>
+      <c r="O26" t="s">
+        <v>45</v>
+      </c>
+      <c r="P26" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q26" t="s">
         <v>20</v>
       </c>
-      <c r="N26" t="s">
-        <v>117</v>
-      </c>
-      <c r="O26" t="s">
-        <v>50</v>
-      </c>
-      <c r="P26" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>24</v>
-      </c>
       <c r="R26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.45">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="2">
         <v>46164.689583333333</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="2">
         <v>46164.690972222219</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E27" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G27" t="s">
-        <v>18</v>
-      </c>
-      <c r="H27" t="s">
-        <v>142</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>143</v>
+        <v>16</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Aisha Tan</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="J27" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="K27" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" t="s">
+        <v>17</v>
+      </c>
+      <c r="M27" t="s">
+        <v>19</v>
+      </c>
+      <c r="N27" t="s">
+        <v>53</v>
+      </c>
+      <c r="O27" t="s">
+        <v>38</v>
+      </c>
+      <c r="P27" t="s">
         <v>30</v>
       </c>
-      <c r="L27" t="s">
-        <v>19</v>
-      </c>
-      <c r="M27" t="s">
-        <v>23</v>
-      </c>
-      <c r="N27" t="s">
-        <v>58</v>
-      </c>
-      <c r="O27" t="s">
-        <v>42</v>
-      </c>
-      <c r="P27" t="s">
-        <v>34</v>
-      </c>
       <c r="Q27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R27" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.45">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="2">
         <v>46164.694444444453</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="2">
         <v>46164.697916666657</v>
       </c>
       <c r="D28" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E28" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G28" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" t="s">
-        <v>145</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>146</v>
+        <v>16</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Raj Ng</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>141</v>
       </c>
       <c r="J28" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="K28" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L28" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M28" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N28" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="O28" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P28" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q28" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="2">
         <v>46164.7</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="2">
         <v>46164.702777777777</v>
       </c>
       <c r="D29" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E29" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="G29" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Ming Koh</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J29" t="s">
+        <v>142</v>
+      </c>
+      <c r="K29" t="s">
         <v>26</v>
       </c>
-      <c r="H29" t="s">
-        <v>148</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="J29" t="s">
-        <v>147</v>
-      </c>
-      <c r="K29" t="s">
-        <v>30</v>
-      </c>
       <c r="L29" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M29" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N29" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="O29" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P29" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q29" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R29" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="2">
         <v>46164.706944444442</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="2">
         <v>46164.709027777782</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E30" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G30" t="s">
+        <v>16</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Kai Williams</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J30" t="s">
+        <v>145</v>
+      </c>
+      <c r="K30" t="s">
+        <v>42</v>
+      </c>
+      <c r="L30" t="s">
+        <v>103</v>
+      </c>
+      <c r="M30" t="s">
         <v>18</v>
       </c>
-      <c r="H30" t="s">
-        <v>151</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="J30" t="s">
-        <v>150</v>
-      </c>
-      <c r="K30" t="s">
-        <v>47</v>
-      </c>
-      <c r="L30" t="s">
-        <v>108</v>
-      </c>
-      <c r="M30" t="s">
-        <v>20</v>
-      </c>
       <c r="N30" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="O30" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P30" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q30" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R30" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>29</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="2">
         <v>46164.710416666669</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="2">
         <v>46164.711805555547</v>
       </c>
       <c r="D31" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E31" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G31" t="s">
-        <v>18</v>
-      </c>
-      <c r="H31" t="s">
-        <v>154</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>155</v>
+        <v>16</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Ting Lee</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>150</v>
       </c>
       <c r="J31" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K31" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L31" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M31" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N31" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O31" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P31" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="Q31" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="R31" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.45">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>30</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="2">
         <v>46164.714583333327</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="2">
         <v>46164.717361111107</v>
       </c>
       <c r="D32" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E32" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G32" t="s">
-        <v>18</v>
-      </c>
-      <c r="H32" t="s">
-        <v>159</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>160</v>
+        <v>16</v>
+      </c>
+      <c r="H32" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Vikram Ong</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>155</v>
       </c>
       <c r="J32" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="K32" t="s">
+        <v>26</v>
+      </c>
+      <c r="L32" t="s">
+        <v>103</v>
+      </c>
+      <c r="M32" t="s">
+        <v>19</v>
+      </c>
+      <c r="N32" t="s">
+        <v>151</v>
+      </c>
+      <c r="O32" t="s">
         <v>30</v>
       </c>
-      <c r="L32" t="s">
-        <v>108</v>
-      </c>
-      <c r="M32" t="s">
-        <v>23</v>
-      </c>
-      <c r="N32" t="s">
-        <v>156</v>
-      </c>
-      <c r="O32" t="s">
-        <v>34</v>
-      </c>
       <c r="P32" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q32" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="R32" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.45">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>31</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="2">
         <v>46164.71875</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="2">
         <v>46164.722222222219</v>
       </c>
       <c r="D33" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E33" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G33" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Yong Ng</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J33" t="s">
+        <v>156</v>
+      </c>
+      <c r="K33" t="s">
+        <v>51</v>
+      </c>
+      <c r="L33" t="s">
+        <v>27</v>
+      </c>
+      <c r="M33" t="s">
         <v>18</v>
       </c>
-      <c r="H33" t="s">
-        <v>162</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="J33" t="s">
-        <v>161</v>
-      </c>
-      <c r="K33" t="s">
-        <v>56</v>
-      </c>
-      <c r="L33" t="s">
-        <v>31</v>
-      </c>
-      <c r="M33" t="s">
+      <c r="N33" t="s">
+        <v>36</v>
+      </c>
+      <c r="O33" t="s">
+        <v>54</v>
+      </c>
+      <c r="P33" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q33" t="s">
         <v>20</v>
       </c>
-      <c r="N33" t="s">
-        <v>40</v>
-      </c>
-      <c r="O33" t="s">
-        <v>59</v>
-      </c>
-      <c r="P33" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>24</v>
-      </c>
       <c r="R33" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="2">
         <v>46164.726388888892</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="2">
         <v>46164.727777777778</v>
       </c>
       <c r="D34" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E34" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G34" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Wei Tan</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="J34" t="s">
+        <v>159</v>
+      </c>
+      <c r="K34" t="s">
         <v>26</v>
       </c>
-      <c r="H34" t="s">
-        <v>165</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="J34" t="s">
-        <v>164</v>
-      </c>
-      <c r="K34" t="s">
-        <v>30</v>
-      </c>
       <c r="L34" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M34" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N34" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="O34" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P34" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="Q34" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R34" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>33</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="2">
         <v>46164.730555555558</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="2">
         <v>46164.732638888891</v>
       </c>
       <c r="D35" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E35" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G35" t="s">
-        <v>18</v>
-      </c>
-      <c r="H35" t="s">
-        <v>168</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>169</v>
+        <v>16</v>
+      </c>
+      <c r="H35" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Xin Williams</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="J35" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="K35" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L35" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M35" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N35" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="O35" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P35" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q35" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R35" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>34</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="2">
         <v>46164.736111111109</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="2">
         <v>46164.738194444442</v>
       </c>
       <c r="D36" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E36" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G36" t="s">
-        <v>18</v>
-      </c>
-      <c r="H36" t="s">
-        <v>171</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>172</v>
+        <v>16</v>
+      </c>
+      <c r="H36" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Ling Chen</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>167</v>
       </c>
       <c r="J36" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="K36" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L36" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M36" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N36" t="s">
+        <v>59</v>
+      </c>
+      <c r="O36" t="s">
         <v>64</v>
       </c>
-      <c r="O36" t="s">
-        <v>69</v>
-      </c>
       <c r="P36" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q36" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R36" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>35</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="2">
         <v>46164.738888888889</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="2">
         <v>46164.741666666669</v>
       </c>
       <c r="D37" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E37" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G37" t="s">
-        <v>18</v>
-      </c>
-      <c r="H37" t="s">
-        <v>174</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>175</v>
+        <v>16</v>
+      </c>
+      <c r="H37" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Sarah Lee</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="J37" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="K37" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L37" t="s">
+        <v>103</v>
+      </c>
+      <c r="M37" t="s">
+        <v>43</v>
+      </c>
+      <c r="N37" t="s">
+        <v>44</v>
+      </c>
+      <c r="O37" t="s">
+        <v>65</v>
+      </c>
+      <c r="P37" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>31</v>
+      </c>
+      <c r="R37" t="s">
         <v>108</v>
       </c>
-      <c r="M37" t="s">
-        <v>48</v>
-      </c>
-      <c r="N37" t="s">
-        <v>49</v>
-      </c>
-      <c r="O37" t="s">
-        <v>70</v>
-      </c>
-      <c r="P37" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>35</v>
-      </c>
-      <c r="R37" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>36</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="2">
         <v>46164.744444444441</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="2">
         <v>46164.746527777781</v>
       </c>
       <c r="D38" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E38" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G38" t="s">
-        <v>18</v>
-      </c>
-      <c r="H38" t="s">
-        <v>177</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>178</v>
+        <v>16</v>
+      </c>
+      <c r="H38" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Kavya Singh</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="J38" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K38" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L38" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="M38" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N38" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O38" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P38" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="Q38" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="R38" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>37</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="2">
         <v>46164.750694444447</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="2">
         <v>46164.754166666673</v>
       </c>
       <c r="D39" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E39" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G39" t="s">
-        <v>18</v>
-      </c>
-      <c r="H39" t="s">
-        <v>180</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>181</v>
+        <v>16</v>
+      </c>
+      <c r="H39" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Mei Kumar</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="J39" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K39" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L39" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M39" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N39" t="s">
+        <v>59</v>
+      </c>
+      <c r="O39" t="s">
+        <v>65</v>
+      </c>
+      <c r="P39" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q39" t="s">
         <v>64</v>
       </c>
-      <c r="O39" t="s">
-        <v>70</v>
-      </c>
-      <c r="P39" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>69</v>
-      </c>
       <c r="R39" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.45">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>38</v>
       </c>
-      <c r="B40" s="3">
+      <c r="B40" s="2">
         <v>46164.75277777778</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="2">
         <v>46164.756249999999</v>
       </c>
       <c r="D40" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E40" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H40" t="s">
-        <v>159</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>183</v>
+        <v>22</v>
+      </c>
+      <c r="H40" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Vikram Ong</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="J40" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="K40" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L40" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="M40" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N40" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="O40" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P40" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q40" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="R40" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>39</v>
       </c>
-      <c r="B41" s="3">
+      <c r="B41" s="2">
         <v>46164.757638888892</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="2">
         <v>46164.761111111111</v>
       </c>
       <c r="D41" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E41" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G41" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Vikram Sharma</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="J41" t="s">
+        <v>179</v>
+      </c>
+      <c r="K41" t="s">
+        <v>85</v>
+      </c>
+      <c r="L41" t="s">
+        <v>52</v>
+      </c>
+      <c r="M41" t="s">
         <v>18</v>
       </c>
-      <c r="H41" t="s">
-        <v>185</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="J41" t="s">
-        <v>184</v>
-      </c>
-      <c r="K41" t="s">
-        <v>90</v>
-      </c>
-      <c r="L41" t="s">
-        <v>57</v>
-      </c>
-      <c r="M41" t="s">
-        <v>20</v>
-      </c>
       <c r="N41" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O41" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P41" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="Q41" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="R41" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>40</v>
       </c>
-      <c r="B42" s="3">
+      <c r="B42" s="2">
         <v>46164.765277777777</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="2">
         <v>46164.768055555563</v>
       </c>
       <c r="D42" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E42" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G42" t="s">
-        <v>18</v>
-      </c>
-      <c r="H42" t="s">
-        <v>188</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>189</v>
+        <v>16</v>
+      </c>
+      <c r="H42" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Ting Williams</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>184</v>
       </c>
       <c r="J42" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="K42" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L42" t="s">
+        <v>27</v>
+      </c>
+      <c r="M42" t="s">
+        <v>43</v>
+      </c>
+      <c r="N42" t="s">
+        <v>70</v>
+      </c>
+      <c r="O42" t="s">
+        <v>30</v>
+      </c>
+      <c r="P42" t="s">
         <v>31</v>
       </c>
-      <c r="M42" t="s">
-        <v>48</v>
-      </c>
-      <c r="N42" t="s">
-        <v>75</v>
-      </c>
-      <c r="O42" t="s">
-        <v>34</v>
-      </c>
-      <c r="P42" t="s">
-        <v>35</v>
-      </c>
       <c r="Q42" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="R42" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.45">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>41</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B43" s="2">
         <v>46164.770138888889</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="2">
         <v>46164.772222222222</v>
       </c>
       <c r="D43" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E43" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G43" t="s">
-        <v>18</v>
-      </c>
-      <c r="H43" t="s">
-        <v>191</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>192</v>
+        <v>16</v>
+      </c>
+      <c r="H43" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Raj Lim</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>187</v>
       </c>
       <c r="J43" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="K43" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L43" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M43" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N43" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O43" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="P43" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="Q43" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="R43" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>42</v>
       </c>
-      <c r="B44" s="3">
+      <c r="B44" s="2">
         <v>46164.773611111108</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="2">
         <v>46164.775694444441</v>
       </c>
       <c r="D44" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E44" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G44" t="s">
-        <v>18</v>
-      </c>
-      <c r="H44" t="s">
-        <v>194</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>195</v>
+        <v>16</v>
+      </c>
+      <c r="H44" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Rui Kumar</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="J44" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K44" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L44" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M44" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N44" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O44" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P44" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q44" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="R44" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.45">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>43</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="2">
         <v>46164.779861111107</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="2">
         <v>46164.783333333333</v>
       </c>
       <c r="D45" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E45" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="G45" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Raj Koh</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="J45" t="s">
+        <v>191</v>
+      </c>
+      <c r="K45" t="s">
+        <v>42</v>
+      </c>
+      <c r="L45" t="s">
+        <v>58</v>
+      </c>
+      <c r="M45" t="s">
         <v>18</v>
       </c>
-      <c r="H45" t="s">
-        <v>197</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="J45" t="s">
-        <v>196</v>
-      </c>
-      <c r="K45" t="s">
-        <v>47</v>
-      </c>
-      <c r="L45" t="s">
-        <v>63</v>
-      </c>
-      <c r="M45" t="s">
-        <v>20</v>
-      </c>
       <c r="N45" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="O45" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="P45" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q45" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="R45" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>44</v>
       </c>
-      <c r="B46" s="3">
+      <c r="B46" s="2">
         <v>46164.783333333333</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="2">
         <v>46164.785416666673</v>
       </c>
       <c r="D46" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E46" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G46" t="s">
-        <v>18</v>
-      </c>
-      <c r="H46" t="s">
-        <v>200</v>
-      </c>
-      <c r="I46" s="5" t="s">
-        <v>201</v>
+        <v>16</v>
+      </c>
+      <c r="H46" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Qi Kumar</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="J46" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="K46" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L46" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M46" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N46" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="O46" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="P46" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="Q46" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="R46" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.45">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>45</v>
       </c>
-      <c r="B47" s="3">
+      <c r="B47" s="2">
         <v>46164.787499999999</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="2">
         <v>46164.790972222218</v>
       </c>
       <c r="D47" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="E47" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G47" t="s">
-        <v>18</v>
-      </c>
-      <c r="H47" t="s">
-        <v>203</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>204</v>
+        <v>16</v>
+      </c>
+      <c r="H47" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Hui Tan</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="J47" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="K47" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L47" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M47" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N47" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="O47" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q47" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="R47" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>46</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B48" s="2">
         <v>46164.793749999997</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="2">
         <v>46164.795138888891</v>
       </c>
       <c r="D48" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E48" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="G48" t="s">
+        <v>16</v>
+      </c>
+      <c r="H48" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Rong Ng</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="J48" t="s">
+        <v>200</v>
+      </c>
+      <c r="K48" t="s">
+        <v>85</v>
+      </c>
+      <c r="L48" t="s">
+        <v>103</v>
+      </c>
+      <c r="M48" t="s">
         <v>18</v>
       </c>
-      <c r="H48" t="s">
-        <v>206</v>
-      </c>
-      <c r="I48" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="J48" t="s">
-        <v>205</v>
-      </c>
-      <c r="K48" t="s">
-        <v>90</v>
-      </c>
-      <c r="L48" t="s">
-        <v>108</v>
-      </c>
-      <c r="M48" t="s">
-        <v>20</v>
-      </c>
       <c r="N48" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O48" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P48" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q48" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="R48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>47</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B49" s="2">
         <v>46164.798611111109</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="2">
         <v>46164.802083333343</v>
       </c>
       <c r="D49" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E49" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G49" t="s">
-        <v>26</v>
-      </c>
-      <c r="H49" t="s">
-        <v>209</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>210</v>
+        <v>22</v>
+      </c>
+      <c r="H49" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Si Williams</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>205</v>
       </c>
       <c r="J49" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="K49" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L49" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M49" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N49" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="O49" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P49" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q49" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="R49" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>48</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B50" s="2">
         <v>46164.803472222222</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="2">
         <v>46164.805555555547</v>
       </c>
       <c r="D50" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E50" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G50" t="s">
-        <v>18</v>
-      </c>
-      <c r="H50" t="s">
-        <v>212</v>
-      </c>
-      <c r="I50" s="5" t="s">
-        <v>213</v>
+        <v>16</v>
+      </c>
+      <c r="H50" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Emma Williams</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="J50" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="K50" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L50" t="s">
+        <v>17</v>
+      </c>
+      <c r="M50" t="s">
         <v>19</v>
       </c>
-      <c r="M50" t="s">
-        <v>23</v>
-      </c>
       <c r="N50" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O50" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="P50" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q50" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="R50" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>49</v>
       </c>
-      <c r="B51" s="3">
+      <c r="B51" s="2">
         <v>46164.806944444441</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="2">
         <v>46164.809027777781</v>
       </c>
       <c r="D51" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E51" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G51" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Sheng Lim</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J51" t="s">
+        <v>209</v>
+      </c>
+      <c r="K51" t="s">
+        <v>51</v>
+      </c>
+      <c r="L51" t="s">
+        <v>27</v>
+      </c>
+      <c r="M51" t="s">
         <v>18</v>
       </c>
-      <c r="H51" t="s">
-        <v>215</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="J51" t="s">
-        <v>214</v>
-      </c>
-      <c r="K51" t="s">
-        <v>56</v>
-      </c>
-      <c r="L51" t="s">
-        <v>31</v>
-      </c>
-      <c r="M51" t="s">
-        <v>20</v>
-      </c>
       <c r="N51" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="O51" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="P51" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q51" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="R51" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>50</v>
       </c>
-      <c r="B52" s="3">
+      <c r="B52" s="2">
         <v>46164.813194444447</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="2">
         <v>46164.814583333333</v>
       </c>
       <c r="D52" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E52" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="G52" t="s">
-        <v>18</v>
-      </c>
-      <c r="H52" t="s">
-        <v>218</v>
-      </c>
-      <c r="I52" s="5" t="s">
-        <v>219</v>
+        <v>16</v>
+      </c>
+      <c r="H52" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Rui Singh</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>214</v>
       </c>
       <c r="J52" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="K52" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L52" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="M52" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N52" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O52" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="P52" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q52" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R52" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>51</v>
       </c>
-      <c r="B53" s="3">
+      <c r="B53" s="2">
         <v>46164.818055555559</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="2">
         <v>46164.820138888892</v>
       </c>
       <c r="D53" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E53" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G53" t="s">
-        <v>18</v>
-      </c>
-      <c r="H53" t="s">
-        <v>221</v>
+        <v>16</v>
+      </c>
+      <c r="H53" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Ming Ng</v>
       </c>
       <c r="I53" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="J53" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="K53" t="s">
+        <v>26</v>
+      </c>
+      <c r="L53" t="s">
+        <v>17</v>
+      </c>
+      <c r="M53" t="s">
+        <v>19</v>
+      </c>
+      <c r="N53" t="s">
+        <v>28</v>
+      </c>
+      <c r="O53" t="s">
+        <v>37</v>
+      </c>
+      <c r="P53" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q53" t="s">
         <v>30</v>
       </c>
-      <c r="L53" t="s">
-        <v>19</v>
-      </c>
-      <c r="M53" t="s">
-        <v>23</v>
-      </c>
-      <c r="N53" t="s">
-        <v>32</v>
-      </c>
-      <c r="O53" t="s">
-        <v>41</v>
-      </c>
-      <c r="P53" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>34</v>
-      </c>
       <c r="R53" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>52</v>
       </c>
-      <c r="B54" s="3">
+      <c r="B54" s="2">
         <v>46164.820833333331</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="2">
         <v>46164.823611111111</v>
       </c>
       <c r="D54" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E54" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G54" t="s">
-        <v>18</v>
-      </c>
-      <c r="H54" t="s">
-        <v>223</v>
+        <v>16</v>
+      </c>
+      <c r="H54" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Jun Kumar</v>
       </c>
       <c r="I54" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="J54" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="K54" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L54" t="s">
+        <v>17</v>
+      </c>
+      <c r="M54" t="s">
         <v>19</v>
       </c>
-      <c r="M54" t="s">
-        <v>23</v>
-      </c>
       <c r="N54" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O54" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P54" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q54" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.45">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>53</v>
       </c>
-      <c r="B55" s="3">
+      <c r="B55" s="2">
         <v>46164.826388888891</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55" s="2">
         <v>46164.829861111109</v>
       </c>
       <c r="D55" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E55" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G55" t="s">
-        <v>18</v>
-      </c>
-      <c r="H55" t="s">
-        <v>225</v>
+        <v>16</v>
+      </c>
+      <c r="H55" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Qi Williams</v>
       </c>
       <c r="I55" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="J55" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="K55" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L55" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="M55" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N55" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="O55" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P55" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="Q55" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R55" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>54</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B56" s="2">
         <v>46164.831250000003</v>
       </c>
-      <c r="C56" s="3">
+      <c r="C56" s="2">
         <v>46164.832638888889</v>
       </c>
       <c r="D56" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E56" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G56" t="s">
-        <v>18</v>
-      </c>
-      <c r="H56" t="s">
-        <v>228</v>
+        <v>16</v>
+      </c>
+      <c r="H56" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Emma Singh</v>
       </c>
       <c r="I56" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="J56" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="K56" t="s">
+        <v>26</v>
+      </c>
+      <c r="L56" t="s">
+        <v>17</v>
+      </c>
+      <c r="M56" t="s">
+        <v>43</v>
+      </c>
+      <c r="N56" t="s">
+        <v>36</v>
+      </c>
+      <c r="O56" t="s">
         <v>30</v>
       </c>
-      <c r="L56" t="s">
-        <v>19</v>
-      </c>
-      <c r="M56" t="s">
-        <v>48</v>
-      </c>
-      <c r="N56" t="s">
-        <v>40</v>
-      </c>
-      <c r="O56" t="s">
-        <v>34</v>
-      </c>
       <c r="P56" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q56" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R56" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.45">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>55</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B57" s="2">
         <v>46164.836111111108</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="2">
         <v>46164.838888888888</v>
       </c>
       <c r="D57" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="E57" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="G57" t="s">
+        <v>16</v>
+      </c>
+      <c r="H57" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Arjun Patel</v>
+      </c>
+      <c r="I57" t="s">
+        <v>227</v>
+      </c>
+      <c r="J57" t="s">
+        <v>225</v>
+      </c>
+      <c r="K57" t="s">
+        <v>42</v>
+      </c>
+      <c r="L57" t="s">
+        <v>103</v>
+      </c>
+      <c r="M57" t="s">
         <v>18</v>
       </c>
-      <c r="H57" t="s">
-        <v>231</v>
-      </c>
-      <c r="I57" t="s">
-        <v>232</v>
-      </c>
-      <c r="J57" t="s">
-        <v>230</v>
-      </c>
-      <c r="K57" t="s">
-        <v>47</v>
-      </c>
-      <c r="L57" t="s">
-        <v>108</v>
-      </c>
-      <c r="M57" t="s">
+      <c r="N57" t="s">
+        <v>59</v>
+      </c>
+      <c r="O57" t="s">
+        <v>37</v>
+      </c>
+      <c r="P57" t="s">
         <v>20</v>
       </c>
-      <c r="N57" t="s">
-        <v>64</v>
-      </c>
-      <c r="O57" t="s">
-        <v>41</v>
-      </c>
-      <c r="P57" t="s">
-        <v>24</v>
-      </c>
       <c r="Q57" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R57" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>56</v>
       </c>
-      <c r="B58" s="3">
+      <c r="B58" s="2">
         <v>46164.842361111107</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="2">
         <v>46164.845138888893</v>
       </c>
       <c r="D58" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E58" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="G58" t="s">
+        <v>16</v>
+      </c>
+      <c r="H58" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Hao Ong</v>
+      </c>
+      <c r="I58" t="s">
+        <v>230</v>
+      </c>
+      <c r="J58" t="s">
+        <v>228</v>
+      </c>
+      <c r="K58" t="s">
+        <v>85</v>
+      </c>
+      <c r="L58" t="s">
+        <v>27</v>
+      </c>
+      <c r="M58" t="s">
         <v>18</v>
       </c>
-      <c r="H58" t="s">
-        <v>234</v>
-      </c>
-      <c r="I58" t="s">
-        <v>235</v>
-      </c>
-      <c r="J58" t="s">
-        <v>233</v>
-      </c>
-      <c r="K58" t="s">
-        <v>90</v>
-      </c>
-      <c r="L58" t="s">
-        <v>31</v>
-      </c>
-      <c r="M58" t="s">
-        <v>20</v>
-      </c>
       <c r="N58" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O58" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P58" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="Q58" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R58" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.45">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>57</v>
       </c>
-      <c r="B59" s="3">
+      <c r="B59" s="2">
         <v>46164.847222222219</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="2">
         <v>46164.848611111112</v>
       </c>
       <c r="D59" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E59" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G59" t="s">
+        <v>16</v>
+      </c>
+      <c r="H59" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Vikram Chua</v>
+      </c>
+      <c r="I59" t="s">
+        <v>233</v>
+      </c>
+      <c r="J59" t="s">
+        <v>231</v>
+      </c>
+      <c r="K59" t="s">
+        <v>26</v>
+      </c>
+      <c r="L59" t="s">
+        <v>27</v>
+      </c>
+      <c r="M59" t="s">
         <v>18</v>
       </c>
-      <c r="H59" t="s">
-        <v>237</v>
-      </c>
-      <c r="I59" t="s">
-        <v>238</v>
-      </c>
-      <c r="J59" t="s">
-        <v>236</v>
-      </c>
-      <c r="K59" t="s">
+      <c r="N59" t="s">
+        <v>98</v>
+      </c>
+      <c r="O59" t="s">
         <v>30</v>
       </c>
-      <c r="L59" t="s">
-        <v>31</v>
-      </c>
-      <c r="M59" t="s">
-        <v>20</v>
-      </c>
-      <c r="N59" t="s">
-        <v>103</v>
-      </c>
-      <c r="O59" t="s">
-        <v>34</v>
-      </c>
       <c r="P59" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q59" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R59" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.45">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>58</v>
       </c>
-      <c r="B60" s="3">
+      <c r="B60" s="2">
         <v>46164.851388888892</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="2">
         <v>46164.854861111111</v>
       </c>
       <c r="D60" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E60" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="G60" t="s">
+        <v>16</v>
+      </c>
+      <c r="H60" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Hao Lee</v>
+      </c>
+      <c r="I60" t="s">
+        <v>236</v>
+      </c>
+      <c r="J60" t="s">
+        <v>234</v>
+      </c>
+      <c r="K60" t="s">
+        <v>26</v>
+      </c>
+      <c r="L60" t="s">
+        <v>27</v>
+      </c>
+      <c r="M60" t="s">
         <v>18</v>
       </c>
-      <c r="H60" t="s">
-        <v>240</v>
-      </c>
-      <c r="I60" t="s">
-        <v>241</v>
-      </c>
-      <c r="J60" t="s">
-        <v>239</v>
-      </c>
-      <c r="K60" t="s">
-        <v>30</v>
-      </c>
-      <c r="L60" t="s">
-        <v>31</v>
-      </c>
-      <c r="M60" t="s">
-        <v>20</v>
-      </c>
       <c r="N60" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="O60" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="P60" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="Q60" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="R60" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.45">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>59</v>
       </c>
-      <c r="B61" s="3">
+      <c r="B61" s="2">
         <v>46164.856249999997</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="2">
         <v>46164.857638888891</v>
       </c>
       <c r="D61" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="E61" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G61" t="s">
-        <v>18</v>
-      </c>
-      <c r="H61" t="s">
-        <v>243</v>
+        <v>16</v>
+      </c>
+      <c r="H61" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Sarah Patel</v>
       </c>
       <c r="I61" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="J61" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="K61" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L61" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M61" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N61" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="O61" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P61" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q61" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="R61" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>60</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B62" s="2">
         <v>46164.861111111109</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62" s="2">
         <v>46164.862500000003</v>
       </c>
       <c r="D62" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E62" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G62" t="s">
-        <v>18</v>
-      </c>
-      <c r="H62" t="s">
-        <v>246</v>
+        <v>16</v>
+      </c>
+      <c r="H62" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Rui Goh</v>
       </c>
       <c r="I62" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="J62" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="K62" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L62" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M62" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N62" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O62" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P62" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q62" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="R62" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.45">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>61</v>
       </c>
-      <c r="B63" s="3">
+      <c r="B63" s="2">
         <v>46164.865972222222</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="2">
         <v>46164.867361111108</v>
       </c>
       <c r="D63" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E63" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="G63" t="s">
-        <v>18</v>
-      </c>
-      <c r="H63" t="s">
-        <v>249</v>
+        <v>16</v>
+      </c>
+      <c r="H63" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Raj Goh</v>
       </c>
       <c r="I63" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="J63" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="K63" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L63" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M63" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N63" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O63" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="P63" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q63" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="R63" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>62</v>
       </c>
-      <c r="B64" s="3">
+      <c r="B64" s="2">
         <v>46164.871527777781</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64" s="2">
         <v>46164.872916666667</v>
       </c>
       <c r="D64" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E64" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="G64" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+      <c r="H64" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Kavya Sharma</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>63</v>
       </c>
-      <c r="B65" s="3">
+      <c r="B65" s="2">
         <v>46164.876388888893</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C65" s="2">
         <v>46164.878472222219</v>
       </c>
       <c r="D65" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E65" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="G65" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+      <c r="H65" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Rong Williams</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>64</v>
       </c>
-      <c r="B66" s="3">
+      <c r="B66" s="2">
         <v>46164.881249999999</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C66" s="2">
         <v>46164.884722222218</v>
       </c>
       <c r="D66" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E66" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="G66" t="s">
+        <v>16</v>
+      </c>
+      <c r="H66" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Rong Williams</v>
+      </c>
+      <c r="I66" t="s">
+        <v>251</v>
+      </c>
+      <c r="J66" t="s">
+        <v>250</v>
+      </c>
+      <c r="K66" t="s">
+        <v>26</v>
+      </c>
+      <c r="L66" t="s">
+        <v>17</v>
+      </c>
+      <c r="M66" t="s">
         <v>18</v>
       </c>
-      <c r="H66" t="s">
-        <v>254</v>
-      </c>
-      <c r="I66" t="s">
-        <v>256</v>
-      </c>
-      <c r="J66" t="s">
-        <v>255</v>
-      </c>
-      <c r="K66" t="s">
-        <v>30</v>
-      </c>
-      <c r="L66" t="s">
-        <v>19</v>
-      </c>
-      <c r="M66" t="s">
-        <v>20</v>
-      </c>
       <c r="N66" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O66" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P66" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="Q66" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="R66" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>65</v>
       </c>
-      <c r="B67" s="3">
+      <c r="B67" s="2">
         <v>46164.884722222218</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67" s="2">
         <v>46164.887499999997</v>
       </c>
       <c r="D67" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E67" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G67" t="s">
-        <v>18</v>
-      </c>
-      <c r="H67" t="s">
-        <v>258</v>
+        <v>16</v>
+      </c>
+      <c r="H67" t="str">
+        <f t="shared" si="0"/>
+        <v>TEST - Qi Tan</v>
       </c>
       <c r="I67" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="J67" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="K67" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L67" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M67" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N67" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O67" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="P67" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="Q67" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="R67" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>66</v>
       </c>
-      <c r="B68" s="3">
+      <c r="B68" s="2">
         <v>46164.89166666667</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68" s="2">
         <v>46164.893750000003</v>
       </c>
       <c r="D68" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E68" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="G68" t="s">
+        <v>16</v>
+      </c>
+      <c r="H68" t="str">
+        <f t="shared" ref="H68:H127" si="1" xml:space="preserve"> _xlfn.CONCAT( "TEST - ", E68)</f>
+        <v>TEST - James Patel</v>
+      </c>
+      <c r="I68" t="s">
+        <v>257</v>
+      </c>
+      <c r="J68" t="s">
+        <v>255</v>
+      </c>
+      <c r="K68" t="s">
+        <v>85</v>
+      </c>
+      <c r="L68" t="s">
+        <v>17</v>
+      </c>
+      <c r="M68" t="s">
         <v>18</v>
       </c>
-      <c r="H68" t="s">
-        <v>261</v>
-      </c>
-      <c r="I68" t="s">
-        <v>262</v>
-      </c>
-      <c r="J68" t="s">
-        <v>260</v>
-      </c>
-      <c r="K68" t="s">
-        <v>90</v>
-      </c>
-      <c r="L68" t="s">
-        <v>19</v>
-      </c>
-      <c r="M68" t="s">
+      <c r="N68" t="s">
+        <v>59</v>
+      </c>
+      <c r="O68" t="s">
         <v>20</v>
       </c>
-      <c r="N68" t="s">
-        <v>64</v>
-      </c>
-      <c r="O68" t="s">
-        <v>24</v>
-      </c>
       <c r="P68" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q68" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="R68" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>67</v>
       </c>
-      <c r="B69" s="3">
+      <c r="B69" s="2">
         <v>46164.895833333343</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C69" s="2">
         <v>46164.899305555547</v>
       </c>
       <c r="D69" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E69" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="G69" t="s">
-        <v>18</v>
-      </c>
-      <c r="H69" t="s">
-        <v>264</v>
+        <v>16</v>
+      </c>
+      <c r="H69" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Tao Lee</v>
       </c>
       <c r="I69" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="J69" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="K69" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L69" t="s">
+        <v>17</v>
+      </c>
+      <c r="M69" t="s">
         <v>19</v>
       </c>
-      <c r="M69" t="s">
-        <v>23</v>
-      </c>
       <c r="N69" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O69" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P69" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q69" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="R69" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.45">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>68</v>
       </c>
-      <c r="B70" s="3">
+      <c r="B70" s="2">
         <v>46164.898611111108</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70" s="2">
         <v>46164.901388888888</v>
       </c>
       <c r="D70" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E70" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G70" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+      <c r="H70" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Yong Kumar</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>69</v>
       </c>
-      <c r="B71" s="3">
+      <c r="B71" s="2">
         <v>46164.90625</v>
       </c>
-      <c r="C71" s="3">
+      <c r="C71" s="2">
         <v>46164.90902777778</v>
       </c>
       <c r="D71" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E71" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G71" t="s">
-        <v>18</v>
-      </c>
-      <c r="H71" t="s">
-        <v>269</v>
+        <v>16</v>
+      </c>
+      <c r="H71" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Yun Tan</v>
       </c>
       <c r="I71" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="J71" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="K71" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L71" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M71" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N71" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="O71" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P71" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q71" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R71" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>70</v>
       </c>
-      <c r="B72" s="3">
+      <c r="B72" s="2">
         <v>46164.90902777778</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72" s="2">
         <v>46164.912499999999</v>
       </c>
       <c r="D72" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E72" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="G72" t="s">
+        <v>16</v>
+      </c>
+      <c r="H72" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Raj Lee</v>
+      </c>
+      <c r="I72" t="s">
+        <v>268</v>
+      </c>
+      <c r="J72" t="s">
+        <v>266</v>
+      </c>
+      <c r="K72" t="s">
+        <v>51</v>
+      </c>
+      <c r="L72" t="s">
+        <v>17</v>
+      </c>
+      <c r="M72" t="s">
         <v>18</v>
       </c>
-      <c r="H72" t="s">
-        <v>272</v>
-      </c>
-      <c r="I72" t="s">
-        <v>273</v>
-      </c>
-      <c r="J72" t="s">
-        <v>271</v>
-      </c>
-      <c r="K72" t="s">
-        <v>56</v>
-      </c>
-      <c r="L72" t="s">
-        <v>19</v>
-      </c>
-      <c r="M72" t="s">
-        <v>20</v>
-      </c>
       <c r="N72" t="s">
+        <v>28</v>
+      </c>
+      <c r="O72" t="s">
+        <v>29</v>
+      </c>
+      <c r="P72" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>86</v>
+      </c>
+      <c r="R72" t="s">
         <v>32</v>
       </c>
-      <c r="O72" t="s">
-        <v>33</v>
-      </c>
-      <c r="P72" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>91</v>
-      </c>
-      <c r="R72" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>71</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B73" s="2">
         <v>46164.914583333331</v>
       </c>
-      <c r="C73" s="3">
+      <c r="C73" s="2">
         <v>46164.918055555558</v>
       </c>
       <c r="D73" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="E73" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G73" t="s">
+        <v>16</v>
+      </c>
+      <c r="H73" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Tao Singh</v>
+      </c>
+      <c r="I73" t="s">
+        <v>271</v>
+      </c>
+      <c r="J73" t="s">
+        <v>269</v>
+      </c>
+      <c r="K73" t="s">
+        <v>51</v>
+      </c>
+      <c r="L73" t="s">
+        <v>58</v>
+      </c>
+      <c r="M73" t="s">
         <v>18</v>
       </c>
-      <c r="H73" t="s">
-        <v>275</v>
-      </c>
-      <c r="I73" t="s">
-        <v>276</v>
-      </c>
-      <c r="J73" t="s">
-        <v>274</v>
-      </c>
-      <c r="K73" t="s">
-        <v>56</v>
-      </c>
-      <c r="L73" t="s">
-        <v>63</v>
-      </c>
-      <c r="M73" t="s">
-        <v>20</v>
-      </c>
       <c r="N73" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O73" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P73" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="Q73" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R73" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>72</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B74" s="2">
         <v>46164.918055555558</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74" s="2">
         <v>46164.920138888891</v>
       </c>
       <c r="D74" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="E74" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="G74" t="s">
-        <v>18</v>
-      </c>
-      <c r="H74" t="s">
-        <v>278</v>
+        <v>16</v>
+      </c>
+      <c r="H74" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Sarah Williams</v>
       </c>
       <c r="I74" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="J74" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="K74" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L74" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M74" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N74" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="O74" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="P74" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q74" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="R74" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>73</v>
       </c>
-      <c r="B75" s="3">
+      <c r="B75" s="2">
         <v>46164.925694444442</v>
       </c>
-      <c r="C75" s="3">
+      <c r="C75" s="2">
         <v>46164.928472222222</v>
       </c>
       <c r="D75" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E75" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G75" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+      <c r="H75" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Qi Sharma</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>74</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B76" s="2">
         <v>46164.928472222222</v>
       </c>
-      <c r="C76" s="3">
+      <c r="C76" s="2">
         <v>46164.929861111108</v>
       </c>
       <c r="D76" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E76" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="G76" t="s">
-        <v>18</v>
-      </c>
-      <c r="H76" t="s">
-        <v>282</v>
+        <v>16</v>
+      </c>
+      <c r="H76" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Mei Koh</v>
       </c>
       <c r="I76" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="J76" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="K76" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L76" t="s">
+        <v>17</v>
+      </c>
+      <c r="M76" t="s">
         <v>19</v>
       </c>
-      <c r="M76" t="s">
-        <v>23</v>
-      </c>
       <c r="N76" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="O76" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="P76" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q76" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R76" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>75</v>
       </c>
-      <c r="B77" s="3">
+      <c r="B77" s="2">
         <v>46164.932638888888</v>
       </c>
-      <c r="C77" s="3">
+      <c r="C77" s="2">
         <v>46164.936111111107</v>
       </c>
       <c r="D77" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="E77" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G77" t="s">
+        <v>16</v>
+      </c>
+      <c r="H77" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Tao Ng</v>
+      </c>
+      <c r="I77" t="s">
+        <v>281</v>
+      </c>
+      <c r="J77" t="s">
+        <v>279</v>
+      </c>
+      <c r="K77" t="s">
+        <v>26</v>
+      </c>
+      <c r="L77" t="s">
+        <v>58</v>
+      </c>
+      <c r="M77" t="s">
         <v>18</v>
       </c>
-      <c r="H77" t="s">
-        <v>285</v>
-      </c>
-      <c r="I77" t="s">
-        <v>286</v>
-      </c>
-      <c r="J77" t="s">
-        <v>284</v>
-      </c>
-      <c r="K77" t="s">
+      <c r="N77" t="s">
+        <v>104</v>
+      </c>
+      <c r="O77" t="s">
+        <v>46</v>
+      </c>
+      <c r="P77" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q77" t="s">
         <v>30</v>
       </c>
-      <c r="L77" t="s">
-        <v>63</v>
-      </c>
-      <c r="M77" t="s">
-        <v>20</v>
-      </c>
-      <c r="N77" t="s">
-        <v>109</v>
-      </c>
-      <c r="O77" t="s">
-        <v>51</v>
-      </c>
-      <c r="P77" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q77" t="s">
-        <v>34</v>
-      </c>
       <c r="R77" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>76</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B78" s="2">
         <v>46164.938194444447</v>
       </c>
-      <c r="C78" s="3">
+      <c r="C78" s="2">
         <v>46164.94027777778</v>
       </c>
       <c r="D78" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E78" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="G78" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+      <c r="H78" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Hao Wong</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>77</v>
       </c>
-      <c r="B79" s="3">
+      <c r="B79" s="2">
         <v>46164.943055555559</v>
       </c>
-      <c r="C79" s="3">
+      <c r="C79" s="2">
         <v>46164.945138888892</v>
       </c>
       <c r="D79" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E79" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="G79" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+      <c r="H79" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Priya Kumar</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>78</v>
       </c>
-      <c r="B80" s="3">
+      <c r="B80" s="2">
         <v>46164.948611111111</v>
       </c>
-      <c r="C80" s="3">
+      <c r="C80" s="2">
         <v>46164.950694444437</v>
       </c>
       <c r="D80" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="E80" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G80" t="s">
-        <v>18</v>
-      </c>
-      <c r="H80" t="s">
-        <v>203</v>
+        <v>16</v>
+      </c>
+      <c r="H80" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Hui Tan</v>
       </c>
       <c r="I80" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="J80" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="K80" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L80" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M80" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N80" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="O80" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P80" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q80" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R80" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>79</v>
       </c>
-      <c r="B81" s="3">
+      <c r="B81" s="2">
         <v>46164.953472222223</v>
       </c>
-      <c r="C81" s="3">
+      <c r="C81" s="2">
         <v>46164.955555555563</v>
       </c>
       <c r="D81" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="E81" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G81" t="s">
-        <v>18</v>
-      </c>
-      <c r="H81" t="s">
-        <v>101</v>
+        <v>16</v>
+      </c>
+      <c r="H81" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Qi Sharma</v>
       </c>
       <c r="I81" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="J81" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="K81" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L81" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M81" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N81" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O81" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="P81" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q81" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R81" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>80</v>
       </c>
-      <c r="B82" s="3">
+      <c r="B82" s="2">
         <v>46164.956944444442</v>
       </c>
-      <c r="C82" s="3">
+      <c r="C82" s="2">
         <v>46164.959027777782</v>
       </c>
       <c r="D82" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E82" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="G82" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+      <c r="H82" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Arjun Ong</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>81</v>
       </c>
-      <c r="B83" s="3">
+      <c r="B83" s="2">
         <v>46164.963888888888</v>
       </c>
-      <c r="C83" s="3">
+      <c r="C83" s="2">
         <v>46164.966666666667</v>
       </c>
       <c r="D83" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="E83" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G83" t="s">
-        <v>18</v>
-      </c>
-      <c r="H83" t="s">
-        <v>228</v>
+        <v>16</v>
+      </c>
+      <c r="H83" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Emma Singh</v>
       </c>
       <c r="I83" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="J83" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="K83" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L83" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="M83" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N83" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="O83" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P83" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="Q83" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="R83" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.45">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>82</v>
       </c>
-      <c r="B84" s="3">
+      <c r="B84" s="2">
         <v>46164.966666666667</v>
       </c>
-      <c r="C84" s="3">
+      <c r="C84" s="2">
         <v>46164.969444444447</v>
       </c>
       <c r="D84" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="E84" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="G84" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+      <c r="H84" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Yun Goh</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>83</v>
       </c>
-      <c r="B85" s="3">
+      <c r="B85" s="2">
         <v>46164.97152777778</v>
       </c>
-      <c r="C85" s="3">
+      <c r="C85" s="2">
         <v>46164.974305555559</v>
       </c>
       <c r="D85" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E85" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="G85" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+      <c r="H85" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Yun Wong</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>84</v>
       </c>
-      <c r="B86" s="3">
+      <c r="B86" s="2">
         <v>46164.978472222218</v>
       </c>
-      <c r="C86" s="3">
+      <c r="C86" s="2">
         <v>46164.981249999997</v>
       </c>
       <c r="D86" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="E86" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="G86" t="s">
-        <v>18</v>
-      </c>
-      <c r="H86" t="s">
-        <v>304</v>
+        <v>16</v>
+      </c>
+      <c r="H86" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Yun Kumar</v>
       </c>
       <c r="I86" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="J86" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="K86" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L86" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M86" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N86" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="O86" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P86" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="Q86" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="R86" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>85</v>
       </c>
-      <c r="B87" s="3">
+      <c r="B87" s="2">
         <v>46164.984027777777</v>
       </c>
-      <c r="C87" s="3">
+      <c r="C87" s="2">
         <v>46164.986111111109</v>
       </c>
       <c r="D87" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="E87" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="G87" t="s">
-        <v>18</v>
-      </c>
-      <c r="H87" t="s">
-        <v>290</v>
+        <v>16</v>
+      </c>
+      <c r="H87" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Priya Kumar</v>
       </c>
       <c r="I87" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="J87" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K87" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L87" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M87" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N87" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O87" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P87" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q87" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R87" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.45">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>86</v>
       </c>
-      <c r="B88" s="3">
+      <c r="B88" s="2">
         <v>46164.986111111109</v>
       </c>
-      <c r="C88" s="3">
+      <c r="C88" s="2">
         <v>46164.989583333343</v>
       </c>
       <c r="D88" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="E88" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="G88" t="s">
-        <v>18</v>
-      </c>
-      <c r="H88" t="s">
-        <v>309</v>
+        <v>16</v>
+      </c>
+      <c r="H88" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Jia Ng</v>
       </c>
       <c r="I88" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="J88" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="K88" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L88" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M88" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N88" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="O88" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P88" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q88" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R88" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>87</v>
       </c>
-      <c r="B89" s="3">
+      <c r="B89" s="2">
         <v>46164.991666666669</v>
       </c>
-      <c r="C89" s="3">
+      <c r="C89" s="2">
         <v>46164.995138888888</v>
       </c>
       <c r="D89" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="E89" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="G89" t="s">
-        <v>18</v>
-      </c>
-      <c r="H89" t="s">
-        <v>312</v>
+        <v>16</v>
+      </c>
+      <c r="H89" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Hui Williams</v>
       </c>
       <c r="I89" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="J89" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="K89" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L89" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M89" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N89" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O89" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P89" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Q89" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="R89" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.45">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>88</v>
       </c>
-      <c r="B90" s="3">
+      <c r="B90" s="2">
         <v>46164.996527777781</v>
       </c>
-      <c r="C90" s="3">
+      <c r="C90" s="2">
         <v>46164.999305555553</v>
       </c>
       <c r="D90" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E90" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G90" t="s">
-        <v>18</v>
-      </c>
-      <c r="H90" t="s">
-        <v>315</v>
+        <v>16</v>
+      </c>
+      <c r="H90" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Ting Goh</v>
       </c>
       <c r="I90" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="J90" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="K90" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L90" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="M90" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N90" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="O90" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q90" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R90" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>89</v>
       </c>
-      <c r="B91" s="3">
+      <c r="B91" s="2">
         <v>46165.00277777778</v>
       </c>
-      <c r="C91" s="3">
+      <c r="C91" s="2">
         <v>46165.004861111112</v>
       </c>
       <c r="D91" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E91" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="G91" t="s">
-        <v>18</v>
-      </c>
-      <c r="H91" t="s">
-        <v>318</v>
+        <v>16</v>
+      </c>
+      <c r="H91" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Hui Chen</v>
       </c>
       <c r="I91" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="J91" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="K91" t="s">
+        <v>26</v>
+      </c>
+      <c r="L91" t="s">
+        <v>27</v>
+      </c>
+      <c r="M91" t="s">
+        <v>19</v>
+      </c>
+      <c r="N91" t="s">
+        <v>98</v>
+      </c>
+      <c r="O91" t="s">
+        <v>29</v>
+      </c>
+      <c r="P91" t="s">
         <v>30</v>
       </c>
-      <c r="L91" t="s">
-        <v>31</v>
-      </c>
-      <c r="M91" t="s">
-        <v>23</v>
-      </c>
-      <c r="N91" t="s">
-        <v>103</v>
-      </c>
-      <c r="O91" t="s">
-        <v>33</v>
-      </c>
-      <c r="P91" t="s">
-        <v>34</v>
-      </c>
       <c r="Q91" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R91" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>90</v>
       </c>
-      <c r="B92" s="3">
+      <c r="B92" s="2">
         <v>46165.006249999999</v>
       </c>
-      <c r="C92" s="3">
+      <c r="C92" s="2">
         <v>46165.009027777778</v>
       </c>
       <c r="D92" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E92" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="G92" t="s">
-        <v>18</v>
-      </c>
-      <c r="H92" t="s">
-        <v>321</v>
+        <v>16</v>
+      </c>
+      <c r="H92" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Rui Williams</v>
       </c>
       <c r="I92" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="J92" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="K92" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L92" t="s">
+        <v>27</v>
+      </c>
+      <c r="M92" t="s">
+        <v>19</v>
+      </c>
+      <c r="N92" t="s">
+        <v>112</v>
+      </c>
+      <c r="O92" t="s">
+        <v>21</v>
+      </c>
+      <c r="P92" t="s">
         <v>31</v>
       </c>
-      <c r="M92" t="s">
-        <v>23</v>
-      </c>
-      <c r="N92" t="s">
-        <v>117</v>
-      </c>
-      <c r="O92" t="s">
-        <v>25</v>
-      </c>
-      <c r="P92" t="s">
-        <v>35</v>
-      </c>
       <c r="Q92" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="R92" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.45">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>91</v>
       </c>
-      <c r="B93" s="3">
+      <c r="B93" s="2">
         <v>46165.013194444437</v>
       </c>
-      <c r="C93" s="3">
+      <c r="C93" s="2">
         <v>46165.015277777777</v>
       </c>
       <c r="D93" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E93" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="G93" t="s">
-        <v>18</v>
-      </c>
-      <c r="H93" t="s">
-        <v>296</v>
+        <v>16</v>
+      </c>
+      <c r="H93" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Arjun Ong</v>
       </c>
       <c r="I93" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="J93" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="K93" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L93" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="M93" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N93" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O93" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="P93" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="Q93" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R93" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>92</v>
       </c>
-      <c r="B94" s="3">
+      <c r="B94" s="2">
         <v>46165.018055555563</v>
       </c>
-      <c r="C94" s="3">
+      <c r="C94" s="2">
         <v>46165.020833333343</v>
       </c>
       <c r="D94" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E94" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="G94" t="s">
+        <v>16</v>
+      </c>
+      <c r="H94" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Tao Ong</v>
+      </c>
+      <c r="I94" t="s">
+        <v>322</v>
+      </c>
+      <c r="J94" t="s">
+        <v>320</v>
+      </c>
+      <c r="K94" t="s">
+        <v>51</v>
+      </c>
+      <c r="L94" t="s">
+        <v>27</v>
+      </c>
+      <c r="M94" t="s">
         <v>18</v>
       </c>
-      <c r="H94" t="s">
-        <v>326</v>
-      </c>
-      <c r="I94" t="s">
-        <v>327</v>
-      </c>
-      <c r="J94" t="s">
-        <v>325</v>
-      </c>
-      <c r="K94" t="s">
-        <v>56</v>
-      </c>
-      <c r="L94" t="s">
-        <v>31</v>
-      </c>
-      <c r="M94" t="s">
-        <v>20</v>
-      </c>
       <c r="N94" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="O94" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="P94" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="Q94" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="R94" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>93</v>
       </c>
-      <c r="B95" s="3">
+      <c r="B95" s="2">
         <v>46165.020138888889</v>
       </c>
-      <c r="C95" s="3">
+      <c r="C95" s="2">
         <v>46165.022916666669</v>
       </c>
       <c r="D95" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E95" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G95" t="s">
-        <v>18</v>
-      </c>
-      <c r="H95" t="s">
-        <v>329</v>
+        <v>16</v>
+      </c>
+      <c r="H95" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Mei Tan</v>
       </c>
       <c r="I95" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="J95" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="K95" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L95" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="M95" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N95" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O95" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P95" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q95" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="R95" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.45">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>94</v>
       </c>
-      <c r="B96" s="3">
+      <c r="B96" s="2">
         <v>46165.025000000001</v>
       </c>
-      <c r="C96" s="3">
+      <c r="C96" s="2">
         <v>46165.027083333327</v>
       </c>
       <c r="D96" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="E96" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="G96" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Wei Koh</v>
+      </c>
+      <c r="I96" t="s">
+        <v>328</v>
+      </c>
+      <c r="J96" t="s">
+        <v>326</v>
+      </c>
+      <c r="K96" t="s">
+        <v>26</v>
+      </c>
+      <c r="L96" t="s">
+        <v>58</v>
+      </c>
+      <c r="M96" t="s">
         <v>18</v>
       </c>
-      <c r="H96" t="s">
-        <v>332</v>
-      </c>
-      <c r="I96" t="s">
-        <v>333</v>
-      </c>
-      <c r="J96" t="s">
-        <v>331</v>
-      </c>
-      <c r="K96" t="s">
-        <v>30</v>
-      </c>
-      <c r="L96" t="s">
-        <v>63</v>
-      </c>
-      <c r="M96" t="s">
-        <v>20</v>
-      </c>
       <c r="N96" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="O96" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="P96" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="Q96" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R96" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>95</v>
       </c>
-      <c r="B97" s="3">
+      <c r="B97" s="2">
         <v>46165.029861111107</v>
       </c>
-      <c r="C97" s="3">
+      <c r="C97" s="2">
         <v>46165.032638888893</v>
       </c>
       <c r="D97" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E97" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="G97" t="s">
-        <v>18</v>
-      </c>
-      <c r="H97" t="s">
-        <v>335</v>
+        <v>16</v>
+      </c>
+      <c r="H97" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Yun Ong</v>
       </c>
       <c r="I97" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="J97" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="K97" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L97" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M97" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N97" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="O97" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P97" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q97" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="R97" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>96</v>
       </c>
-      <c r="B98" s="3">
+      <c r="B98" s="2">
         <v>46165.036805555559</v>
       </c>
-      <c r="C98" s="3">
+      <c r="C98" s="2">
         <v>46165.038888888892</v>
       </c>
       <c r="D98" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="E98" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G98" t="s">
-        <v>18</v>
-      </c>
-      <c r="H98" t="s">
-        <v>243</v>
+        <v>16</v>
+      </c>
+      <c r="H98" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Sarah Patel</v>
       </c>
       <c r="I98" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="J98" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="K98" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L98" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="M98" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N98" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="O98" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P98" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q98" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="R98" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.45">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>97</v>
       </c>
-      <c r="B99" s="3">
+      <c r="B99" s="2">
         <v>46165.040972222218</v>
       </c>
-      <c r="C99" s="3">
+      <c r="C99" s="2">
         <v>46165.042361111111</v>
       </c>
       <c r="D99" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="E99" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="G99" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>98</v>
       </c>
-      <c r="B100" s="3">
+      <c r="B100" s="2">
         <v>46165.046527777777</v>
       </c>
-      <c r="C100" s="3">
+      <c r="C100" s="2">
         <v>46165.05</v>
       </c>
       <c r="D100" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E100" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="G100" t="s">
-        <v>18</v>
-      </c>
-      <c r="H100" t="s">
-        <v>342</v>
+        <v>16</v>
+      </c>
+      <c r="H100" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Mei Goh</v>
       </c>
       <c r="I100" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="J100" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="K100" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L100" t="s">
+        <v>17</v>
+      </c>
+      <c r="M100" t="s">
         <v>19</v>
       </c>
-      <c r="M100" t="s">
-        <v>23</v>
-      </c>
       <c r="N100" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="O100" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P100" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="Q100" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R100" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.45">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>99</v>
       </c>
-      <c r="B101" s="3">
+      <c r="B101" s="2">
         <v>46165.052083333343</v>
       </c>
-      <c r="C101" s="3">
+      <c r="C101" s="2">
         <v>46165.054166666669</v>
       </c>
       <c r="D101" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="E101" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="G101" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+      <c r="H101" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Ting Chen</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>100</v>
       </c>
-      <c r="B102" s="3">
+      <c r="B102" s="2">
         <v>46165.054166666669</v>
       </c>
-      <c r="C102" s="3">
+      <c r="C102" s="2">
         <v>46165.056944444441</v>
       </c>
       <c r="D102" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="E102" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="G102" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+      <c r="H102" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Emma Tan</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>101</v>
       </c>
-      <c r="B103" s="3">
+      <c r="B103" s="2">
         <v>46165.061805555553</v>
       </c>
-      <c r="C103" s="3">
+      <c r="C103" s="2">
         <v>46165.063194444447</v>
       </c>
       <c r="D103" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="E103" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="G103" t="s">
+        <v>16</v>
+      </c>
+      <c r="H103" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Yong Koh</v>
+      </c>
+      <c r="I103" t="s">
+        <v>345</v>
+      </c>
+      <c r="J103" t="s">
+        <v>343</v>
+      </c>
+      <c r="K103" t="s">
+        <v>42</v>
+      </c>
+      <c r="L103" t="s">
+        <v>27</v>
+      </c>
+      <c r="M103" t="s">
         <v>18</v>
       </c>
-      <c r="H103" t="s">
-        <v>349</v>
-      </c>
-      <c r="I103" t="s">
-        <v>350</v>
-      </c>
-      <c r="J103" t="s">
-        <v>348</v>
-      </c>
-      <c r="K103" t="s">
-        <v>47</v>
-      </c>
-      <c r="L103" t="s">
-        <v>31</v>
-      </c>
-      <c r="M103" t="s">
-        <v>20</v>
-      </c>
       <c r="N103" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="O103" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P103" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="Q103" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="R103" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>102</v>
       </c>
-      <c r="B104" s="3">
+      <c r="B104" s="2">
         <v>46165.065972222219</v>
       </c>
-      <c r="C104" s="3">
+      <c r="C104" s="2">
         <v>46165.069444444453</v>
       </c>
       <c r="D104" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="E104" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="G104" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+      <c r="H104" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Kavya Goh</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>103</v>
       </c>
-      <c r="B105" s="3">
+      <c r="B105" s="2">
         <v>46165.070833333331</v>
       </c>
-      <c r="C105" s="3">
+      <c r="C105" s="2">
         <v>46165.072916666657</v>
       </c>
       <c r="D105" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E105" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G105" t="s">
+        <v>16</v>
+      </c>
+      <c r="H105" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Tao Ng</v>
+      </c>
+      <c r="I105" t="s">
+        <v>349</v>
+      </c>
+      <c r="J105" t="s">
+        <v>348</v>
+      </c>
+      <c r="K105" t="s">
+        <v>85</v>
+      </c>
+      <c r="L105" t="s">
+        <v>52</v>
+      </c>
+      <c r="M105" t="s">
         <v>18</v>
       </c>
-      <c r="H105" t="s">
-        <v>285</v>
-      </c>
-      <c r="I105" t="s">
-        <v>354</v>
-      </c>
-      <c r="J105" t="s">
-        <v>353</v>
-      </c>
-      <c r="K105" t="s">
-        <v>90</v>
-      </c>
-      <c r="L105" t="s">
-        <v>57</v>
-      </c>
-      <c r="M105" t="s">
-        <v>20</v>
-      </c>
       <c r="N105" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="O105" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P105" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="Q105" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="R105" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.45">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>104</v>
       </c>
-      <c r="B106" s="3">
+      <c r="B106" s="2">
         <v>46165.073611111111</v>
       </c>
-      <c r="C106" s="3">
+      <c r="C106" s="2">
         <v>46165.074999999997</v>
       </c>
       <c r="D106" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E106" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G106" t="s">
+        <v>16</v>
+      </c>
+      <c r="H106" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Vikram Chua</v>
+      </c>
+      <c r="I106" t="s">
+        <v>351</v>
+      </c>
+      <c r="J106" t="s">
+        <v>350</v>
+      </c>
+      <c r="K106" t="s">
+        <v>85</v>
+      </c>
+      <c r="L106" t="s">
+        <v>52</v>
+      </c>
+      <c r="M106" t="s">
         <v>18</v>
       </c>
-      <c r="H106" t="s">
-        <v>237</v>
-      </c>
-      <c r="I106" t="s">
-        <v>356</v>
-      </c>
-      <c r="J106" t="s">
-        <v>355</v>
-      </c>
-      <c r="K106" t="s">
-        <v>90</v>
-      </c>
-      <c r="L106" t="s">
-        <v>57</v>
-      </c>
-      <c r="M106" t="s">
-        <v>20</v>
-      </c>
       <c r="N106" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="O106" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="P106" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q106" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R106" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>105</v>
       </c>
-      <c r="B107" s="3">
+      <c r="B107" s="2">
         <v>46165.078472222223</v>
       </c>
-      <c r="C107" s="3">
+      <c r="C107" s="2">
         <v>46165.081250000003</v>
       </c>
       <c r="D107" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E107" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="G107" t="s">
-        <v>18</v>
-      </c>
-      <c r="H107" t="s">
-        <v>321</v>
+        <v>16</v>
+      </c>
+      <c r="H107" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Rui Williams</v>
       </c>
       <c r="I107" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="J107" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="K107" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L107" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M107" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N107" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="O107" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P107" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q107" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="R107" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>106</v>
       </c>
-      <c r="B108" s="3">
+      <c r="B108" s="2">
         <v>46165.084722222222</v>
       </c>
-      <c r="C108" s="3">
+      <c r="C108" s="2">
         <v>46165.086805555547</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="E108" t="s">
+        <v>24</v>
+      </c>
+      <c r="G108" t="s">
+        <v>16</v>
+      </c>
+      <c r="H108" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Jia Tan</v>
+      </c>
+      <c r="I108" t="s">
+        <v>355</v>
+      </c>
+      <c r="J108" t="s">
+        <v>354</v>
+      </c>
+      <c r="K108" t="s">
+        <v>26</v>
+      </c>
+      <c r="L108" t="s">
+        <v>58</v>
+      </c>
+      <c r="M108" t="s">
+        <v>19</v>
+      </c>
+      <c r="N108" t="s">
         <v>28</v>
       </c>
-      <c r="G108" t="s">
-        <v>18</v>
-      </c>
-      <c r="H108" t="s">
-        <v>28</v>
-      </c>
-      <c r="I108" t="s">
-        <v>360</v>
-      </c>
-      <c r="J108" t="s">
-        <v>359</v>
-      </c>
-      <c r="K108" t="s">
+      <c r="O108" t="s">
+        <v>29</v>
+      </c>
+      <c r="P108" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q108" t="s">
         <v>30</v>
       </c>
-      <c r="L108" t="s">
-        <v>63</v>
-      </c>
-      <c r="M108" t="s">
-        <v>23</v>
-      </c>
-      <c r="N108" t="s">
+      <c r="R108" t="s">
         <v>32</v>
       </c>
-      <c r="O108" t="s">
-        <v>33</v>
-      </c>
-      <c r="P108" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q108" t="s">
-        <v>34</v>
-      </c>
-      <c r="R108" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>107</v>
       </c>
-      <c r="B109" s="3">
+      <c r="B109" s="2">
         <v>46165.088194444441</v>
       </c>
-      <c r="C109" s="3">
+      <c r="C109" s="2">
         <v>46165.09097222222</v>
       </c>
       <c r="D109" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="E109" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="G109" t="s">
+        <v>16</v>
+      </c>
+      <c r="H109" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - James Lee</v>
+      </c>
+      <c r="I109" t="s">
+        <v>358</v>
+      </c>
+      <c r="J109" t="s">
+        <v>356</v>
+      </c>
+      <c r="K109" t="s">
+        <v>42</v>
+      </c>
+      <c r="L109" t="s">
+        <v>17</v>
+      </c>
+      <c r="M109" t="s">
         <v>18</v>
       </c>
-      <c r="H109" t="s">
-        <v>362</v>
-      </c>
-      <c r="I109" t="s">
-        <v>363</v>
-      </c>
-      <c r="J109" t="s">
-        <v>361</v>
-      </c>
-      <c r="K109" t="s">
-        <v>47</v>
-      </c>
-      <c r="L109" t="s">
-        <v>19</v>
-      </c>
-      <c r="M109" t="s">
-        <v>20</v>
-      </c>
       <c r="N109" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="O109" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P109" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q109" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="R109" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.45">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>108</v>
       </c>
-      <c r="B110" s="3">
+      <c r="B110" s="2">
         <v>46165.093055555553</v>
       </c>
-      <c r="C110" s="3">
+      <c r="C110" s="2">
         <v>46165.095833333333</v>
       </c>
       <c r="D110" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="E110" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G110" t="s">
-        <v>18</v>
-      </c>
-      <c r="H110" t="s">
-        <v>101</v>
+        <v>16</v>
+      </c>
+      <c r="H110" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Qi Sharma</v>
       </c>
       <c r="I110" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="J110" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="K110" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L110" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="M110" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N110" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="O110" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="P110" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="Q110" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R110" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>109</v>
       </c>
-      <c r="B111" s="3">
+      <c r="B111" s="2">
         <v>46165.099305555559</v>
       </c>
-      <c r="C111" s="3">
+      <c r="C111" s="2">
         <v>46165.102083333331</v>
       </c>
       <c r="D111" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="E111" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G111" t="s">
+        <v>16</v>
+      </c>
+      <c r="H111" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Yong Chua</v>
+      </c>
+      <c r="I111" t="s">
+        <v>363</v>
+      </c>
+      <c r="J111" t="s">
+        <v>361</v>
+      </c>
+      <c r="K111" t="s">
+        <v>51</v>
+      </c>
+      <c r="L111" t="s">
+        <v>52</v>
+      </c>
+      <c r="M111" t="s">
         <v>18</v>
       </c>
-      <c r="H111" t="s">
-        <v>367</v>
-      </c>
-      <c r="I111" t="s">
-        <v>368</v>
-      </c>
-      <c r="J111" t="s">
-        <v>366</v>
-      </c>
-      <c r="K111" t="s">
-        <v>56</v>
-      </c>
-      <c r="L111" t="s">
-        <v>57</v>
-      </c>
-      <c r="M111" t="s">
-        <v>20</v>
-      </c>
       <c r="N111" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="O111" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="P111" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q111" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="R111" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>110</v>
       </c>
-      <c r="B112" s="3">
+      <c r="B112" s="2">
         <v>46165.103472222218</v>
       </c>
-      <c r="C112" s="3">
+      <c r="C112" s="2">
         <v>46165.106249999997</v>
       </c>
       <c r="D112" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E112" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="G112" t="s">
+        <v>16</v>
+      </c>
+      <c r="H112" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Hao Ng</v>
+      </c>
+      <c r="I112" t="s">
+        <v>366</v>
+      </c>
+      <c r="J112" t="s">
+        <v>364</v>
+      </c>
+      <c r="K112" t="s">
+        <v>26</v>
+      </c>
+      <c r="L112" t="s">
+        <v>52</v>
+      </c>
+      <c r="M112" t="s">
         <v>18</v>
       </c>
-      <c r="H112" t="s">
-        <v>370</v>
-      </c>
-      <c r="I112" t="s">
-        <v>371</v>
-      </c>
-      <c r="J112" t="s">
-        <v>369</v>
-      </c>
-      <c r="K112" t="s">
+      <c r="N112" t="s">
+        <v>36</v>
+      </c>
+      <c r="O112" t="s">
+        <v>37</v>
+      </c>
+      <c r="P112" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q112" t="s">
         <v>30</v>
       </c>
-      <c r="L112" t="s">
-        <v>57</v>
-      </c>
-      <c r="M112" t="s">
-        <v>20</v>
-      </c>
-      <c r="N112" t="s">
-        <v>40</v>
-      </c>
-      <c r="O112" t="s">
-        <v>41</v>
-      </c>
-      <c r="P112" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q112" t="s">
-        <v>34</v>
-      </c>
       <c r="R112" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>111</v>
       </c>
-      <c r="B113" s="3">
+      <c r="B113" s="2">
         <v>46165.109722222223</v>
       </c>
-      <c r="C113" s="3">
+      <c r="C113" s="2">
         <v>46165.111111111109</v>
       </c>
       <c r="D113" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E113" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="G113" t="s">
-        <v>18</v>
-      </c>
-      <c r="H113" t="s">
-        <v>315</v>
+        <v>16</v>
+      </c>
+      <c r="H113" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Ting Goh</v>
       </c>
       <c r="I113" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="J113" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="K113" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="L113" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M113" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N113" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="O113" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P113" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="Q113" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="R113" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>112</v>
       </c>
-      <c r="B114" s="3">
+      <c r="B114" s="2">
         <v>46165.113194444442</v>
       </c>
-      <c r="C114" s="3">
+      <c r="C114" s="2">
         <v>46165.115972222222</v>
       </c>
       <c r="D114" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E114" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G114" t="s">
+        <v>16</v>
+      </c>
+      <c r="H114" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Sheng Lim</v>
+      </c>
+      <c r="I114" t="s">
+        <v>370</v>
+      </c>
+      <c r="J114" t="s">
+        <v>369</v>
+      </c>
+      <c r="K114" t="s">
+        <v>26</v>
+      </c>
+      <c r="L114" t="s">
+        <v>103</v>
+      </c>
+      <c r="M114" t="s">
         <v>18</v>
       </c>
-      <c r="H114" t="s">
-        <v>215</v>
-      </c>
-      <c r="I114" t="s">
-        <v>375</v>
-      </c>
-      <c r="J114" t="s">
-        <v>374</v>
-      </c>
-      <c r="K114" t="s">
+      <c r="N114" t="s">
+        <v>59</v>
+      </c>
+      <c r="O114" t="s">
+        <v>46</v>
+      </c>
+      <c r="P114" t="s">
         <v>30</v>
       </c>
-      <c r="L114" t="s">
-        <v>108</v>
-      </c>
-      <c r="M114" t="s">
-        <v>20</v>
-      </c>
-      <c r="N114" t="s">
-        <v>64</v>
-      </c>
-      <c r="O114" t="s">
-        <v>51</v>
-      </c>
-      <c r="P114" t="s">
-        <v>34</v>
-      </c>
       <c r="Q114" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R114" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>113</v>
       </c>
-      <c r="B115" s="3">
+      <c r="B115" s="2">
         <v>46165.120138888888</v>
       </c>
-      <c r="C115" s="3">
+      <c r="C115" s="2">
         <v>46165.121527777781</v>
       </c>
       <c r="D115" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="E115" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="G115" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>114</v>
       </c>
-      <c r="B116" s="3">
+      <c r="B116" s="2">
         <v>46165.125</v>
       </c>
-      <c r="C116" s="3">
+      <c r="C116" s="2">
         <v>46165.126388888893</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="E116" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="G116" t="s">
+        <v>16</v>
+      </c>
+      <c r="H116" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Wei Patel</v>
+      </c>
+      <c r="I116" t="s">
+        <v>375</v>
+      </c>
+      <c r="J116" t="s">
+        <v>373</v>
+      </c>
+      <c r="K116" t="s">
+        <v>42</v>
+      </c>
+      <c r="L116" t="s">
+        <v>58</v>
+      </c>
+      <c r="M116" t="s">
         <v>18</v>
       </c>
-      <c r="H116" t="s">
-        <v>379</v>
-      </c>
-      <c r="I116" t="s">
-        <v>380</v>
-      </c>
-      <c r="J116" t="s">
-        <v>378</v>
-      </c>
-      <c r="K116" t="s">
-        <v>47</v>
-      </c>
-      <c r="L116" t="s">
-        <v>63</v>
-      </c>
-      <c r="M116" t="s">
-        <v>20</v>
-      </c>
       <c r="N116" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="O116" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="P116" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q116" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="R116" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>115</v>
       </c>
-      <c r="B117" s="3">
+      <c r="B117" s="2">
         <v>46165.127083333333</v>
       </c>
-      <c r="C117" s="3">
+      <c r="C117" s="2">
         <v>46165.129861111112</v>
       </c>
       <c r="D117" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E117" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="G117" t="s">
+        <v>16</v>
+      </c>
+      <c r="H117" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Tao Koh</v>
+      </c>
+      <c r="I117" t="s">
+        <v>378</v>
+      </c>
+      <c r="J117" t="s">
+        <v>376</v>
+      </c>
+      <c r="K117" t="s">
+        <v>51</v>
+      </c>
+      <c r="L117" t="s">
+        <v>27</v>
+      </c>
+      <c r="M117" t="s">
         <v>18</v>
       </c>
-      <c r="H117" t="s">
-        <v>382</v>
-      </c>
-      <c r="I117" t="s">
-        <v>383</v>
-      </c>
-      <c r="J117" t="s">
-        <v>381</v>
-      </c>
-      <c r="K117" t="s">
-        <v>56</v>
-      </c>
-      <c r="L117" t="s">
+      <c r="N117" t="s">
+        <v>28</v>
+      </c>
+      <c r="O117" t="s">
+        <v>29</v>
+      </c>
+      <c r="P117" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q117" t="s">
         <v>31</v>
       </c>
-      <c r="M117" t="s">
-        <v>20</v>
-      </c>
-      <c r="N117" t="s">
+      <c r="R117" t="s">
         <v>32</v>
       </c>
-      <c r="O117" t="s">
-        <v>33</v>
-      </c>
-      <c r="P117" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q117" t="s">
-        <v>35</v>
-      </c>
-      <c r="R117" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>116</v>
       </c>
-      <c r="B118" s="3">
+      <c r="B118" s="2">
         <v>46165.132638888892</v>
       </c>
-      <c r="C118" s="3">
+      <c r="C118" s="2">
         <v>46165.135416666657</v>
       </c>
       <c r="D118" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="E118" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="G118" t="s">
-        <v>18</v>
-      </c>
-      <c r="H118" t="s">
-        <v>385</v>
+        <v>16</v>
+      </c>
+      <c r="H118" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Sarah Ng</v>
       </c>
       <c r="I118" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="J118" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="K118" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L118" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M118" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N118" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="O118" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P118" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q118" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R118" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.45">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>117</v>
       </c>
-      <c r="B119" s="3">
+      <c r="B119" s="2">
         <v>46165.137499999997</v>
       </c>
-      <c r="C119" s="3">
+      <c r="C119" s="2">
         <v>46165.140972222223</v>
       </c>
       <c r="D119" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="E119" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G119" t="s">
-        <v>18</v>
-      </c>
-      <c r="H119" t="s">
-        <v>269</v>
+        <v>16</v>
+      </c>
+      <c r="H119" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Yun Tan</v>
       </c>
       <c r="I119" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="J119" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="K119" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L119" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="M119" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N119" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="O119" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P119" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q119" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="R119" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>118</v>
       </c>
-      <c r="B120" s="3">
+      <c r="B120" s="2">
         <v>46165.143055555563</v>
       </c>
-      <c r="C120" s="3">
+      <c r="C120" s="2">
         <v>46165.144444444442</v>
       </c>
       <c r="D120" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E120" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="G120" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>119</v>
       </c>
-      <c r="B121" s="3">
+      <c r="B121" s="2">
         <v>46165.147222222222</v>
       </c>
-      <c r="C121" s="3">
+      <c r="C121" s="2">
         <v>46165.148611111108</v>
       </c>
       <c r="D121" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E121" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="G121" t="s">
-        <v>18</v>
-      </c>
-      <c r="H121" t="s">
-        <v>288</v>
+        <v>16</v>
+      </c>
+      <c r="H121" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Hao Wong</v>
       </c>
       <c r="I121" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="J121" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="K121" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L121" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M121" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N121" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O121" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P121" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q121" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="R121" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.45">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>120</v>
       </c>
-      <c r="B122" s="3">
+      <c r="B122" s="2">
         <v>46165.154166666667</v>
       </c>
-      <c r="C122" s="3">
+      <c r="C122" s="2">
         <v>46165.157638888893</v>
       </c>
       <c r="D122" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="E122" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="G122" t="s">
+        <v>16</v>
+      </c>
+      <c r="H122" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Rong Goh</v>
+      </c>
+      <c r="I122" t="s">
+        <v>389</v>
+      </c>
+      <c r="J122" t="s">
+        <v>387</v>
+      </c>
+      <c r="K122" t="s">
+        <v>42</v>
+      </c>
+      <c r="L122" t="s">
+        <v>52</v>
+      </c>
+      <c r="M122" t="s">
         <v>18</v>
       </c>
-      <c r="H122" t="s">
-        <v>393</v>
-      </c>
-      <c r="I122" t="s">
-        <v>394</v>
-      </c>
-      <c r="J122" t="s">
-        <v>392</v>
-      </c>
-      <c r="K122" t="s">
+      <c r="N122" t="s">
+        <v>44</v>
+      </c>
+      <c r="O122" t="s">
+        <v>45</v>
+      </c>
+      <c r="P122" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>46</v>
+      </c>
+      <c r="R122" t="s">
         <v>47</v>
       </c>
-      <c r="L122" t="s">
-        <v>57</v>
-      </c>
-      <c r="M122" t="s">
-        <v>20</v>
-      </c>
-      <c r="N122" t="s">
-        <v>49</v>
-      </c>
-      <c r="O122" t="s">
-        <v>50</v>
-      </c>
-      <c r="P122" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q122" t="s">
-        <v>51</v>
-      </c>
-      <c r="R122" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>121</v>
       </c>
-      <c r="B123" s="3">
+      <c r="B123" s="2">
         <v>46165.158333333333</v>
       </c>
-      <c r="C123" s="3">
+      <c r="C123" s="2">
         <v>46165.161111111112</v>
       </c>
       <c r="D123" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E123" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="G123" t="s">
+        <v>16</v>
+      </c>
+      <c r="H123" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Hao Lim</v>
+      </c>
+      <c r="I123" t="s">
+        <v>392</v>
+      </c>
+      <c r="J123" t="s">
+        <v>390</v>
+      </c>
+      <c r="K123" t="s">
+        <v>85</v>
+      </c>
+      <c r="L123" t="s">
+        <v>103</v>
+      </c>
+      <c r="M123" t="s">
         <v>18</v>
       </c>
-      <c r="H123" t="s">
-        <v>396</v>
-      </c>
-      <c r="I123" t="s">
-        <v>397</v>
-      </c>
-      <c r="J123" t="s">
-        <v>395</v>
-      </c>
-      <c r="K123" t="s">
-        <v>90</v>
-      </c>
-      <c r="L123" t="s">
-        <v>108</v>
-      </c>
-      <c r="M123" t="s">
-        <v>20</v>
-      </c>
       <c r="N123" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="O123" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P123" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="Q123" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R123" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>122</v>
       </c>
-      <c r="B124" s="3">
+      <c r="B124" s="2">
         <v>46165.161805555559</v>
       </c>
-      <c r="C124" s="3">
+      <c r="C124" s="2">
         <v>46165.163888888892</v>
       </c>
       <c r="D124" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E124" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="G124" t="s">
-        <v>18</v>
-      </c>
-      <c r="H124" t="s">
-        <v>304</v>
+        <v>16</v>
+      </c>
+      <c r="H124" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Yun Kumar</v>
       </c>
       <c r="I124" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="J124" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K124" t="s">
+        <v>42</v>
+      </c>
+      <c r="L124" t="s">
+        <v>58</v>
+      </c>
+      <c r="M124" t="s">
+        <v>43</v>
+      </c>
+      <c r="N124" t="s">
+        <v>28</v>
+      </c>
+      <c r="O124" t="s">
+        <v>45</v>
+      </c>
+      <c r="P124" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>31</v>
+      </c>
+      <c r="R124" t="s">
         <v>47</v>
       </c>
-      <c r="L124" t="s">
-        <v>63</v>
-      </c>
-      <c r="M124" t="s">
-        <v>48</v>
-      </c>
-      <c r="N124" t="s">
-        <v>32</v>
-      </c>
-      <c r="O124" t="s">
-        <v>50</v>
-      </c>
-      <c r="P124" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q124" t="s">
-        <v>35</v>
-      </c>
-      <c r="R124" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>123</v>
       </c>
-      <c r="B125" s="3">
+      <c r="B125" s="2">
         <v>46165.168055555558</v>
       </c>
-      <c r="C125" s="3">
+      <c r="C125" s="2">
         <v>46165.170138888891</v>
       </c>
       <c r="D125" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E125" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="G125" t="s">
-        <v>18</v>
-      </c>
-      <c r="H125" t="s">
-        <v>401</v>
+        <v>16</v>
+      </c>
+      <c r="H125" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Ting Ong</v>
       </c>
       <c r="I125" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="J125" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="K125" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L125" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M125" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N125" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O125" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P125" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q125" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="R125" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.45">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>124</v>
       </c>
-      <c r="B126" s="3">
+      <c r="B126" s="2">
         <v>46165.17291666667</v>
       </c>
-      <c r="C126" s="3">
+      <c r="C126" s="2">
         <v>46165.174305555563</v>
       </c>
       <c r="D126" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="E126" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="G126" t="s">
-        <v>18</v>
-      </c>
-      <c r="H126" t="s">
-        <v>404</v>
+        <v>16</v>
+      </c>
+      <c r="H126" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Kavya Lim</v>
       </c>
       <c r="I126" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="J126" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="K126" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L126" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="M126" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N126" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O126" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="P126" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q126" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="R126" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>125</v>
       </c>
-      <c r="B127" s="3">
+      <c r="B127" s="2">
         <v>46165.176388888889</v>
       </c>
-      <c r="C127" s="3">
+      <c r="C127" s="2">
         <v>46165.179166666669</v>
       </c>
       <c r="D127" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E127" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="G127" t="s">
-        <v>18</v>
-      </c>
-      <c r="H127" t="s">
-        <v>407</v>
+        <v>16</v>
+      </c>
+      <c r="H127" t="str">
+        <f t="shared" si="1"/>
+        <v>TEST - Xin Lee</v>
       </c>
       <c r="I127" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="J127" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="K127" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L127" t="s">
+        <v>103</v>
+      </c>
+      <c r="M127" t="s">
+        <v>19</v>
+      </c>
+      <c r="N127" t="s">
+        <v>36</v>
+      </c>
+      <c r="O127" t="s">
+        <v>65</v>
+      </c>
+      <c r="P127" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>38</v>
+      </c>
+      <c r="R127" t="s">
         <v>108</v>
-      </c>
-      <c r="M127" t="s">
-        <v>23</v>
-      </c>
-      <c r="N127" t="s">
-        <v>40</v>
-      </c>
-      <c r="O127" t="s">
-        <v>70</v>
-      </c>
-      <c r="P127" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q127" t="s">
-        <v>42</v>
-      </c>
-      <c r="R127" t="s">
-        <v>113</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>